--- a/output/version3/test/20-10/MARL/CTDE/RL-RL with CL/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-10/MARL/CTDE/RL-RL with CL/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>912</v>
+        <v>1016</v>
       </c>
       <c r="C2" t="n">
-        <v>887</v>
+        <v>1129</v>
       </c>
       <c r="D2" t="n">
-        <v>1031</v>
+        <v>1109</v>
       </c>
       <c r="E2" t="n">
-        <v>1071</v>
+        <v>965</v>
       </c>
       <c r="F2" t="n">
-        <v>894</v>
+        <v>962</v>
       </c>
       <c r="G2" t="n">
-        <v>1042</v>
+        <v>990</v>
       </c>
       <c r="H2" t="n">
-        <v>983</v>
+        <v>901</v>
       </c>
       <c r="I2" t="n">
-        <v>1025</v>
+        <v>988</v>
       </c>
       <c r="J2" t="n">
-        <v>913</v>
+        <v>981</v>
       </c>
       <c r="K2" t="n">
-        <v>1164</v>
+        <v>986</v>
       </c>
       <c r="L2" t="n">
-        <v>992.2</v>
+        <v>1002.7</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>1095</v>
+        <v>994</v>
       </c>
       <c r="C3" t="n">
-        <v>1225</v>
+        <v>890</v>
       </c>
       <c r="D3" t="n">
-        <v>1035</v>
+        <v>1065</v>
       </c>
       <c r="E3" t="n">
-        <v>910</v>
+        <v>868</v>
       </c>
       <c r="F3" t="n">
-        <v>929</v>
+        <v>1069</v>
       </c>
       <c r="G3" t="n">
-        <v>1003</v>
+        <v>930</v>
       </c>
       <c r="H3" t="n">
-        <v>949</v>
+        <v>996</v>
       </c>
       <c r="I3" t="n">
-        <v>972</v>
+        <v>960</v>
       </c>
       <c r="J3" t="n">
-        <v>933</v>
+        <v>1046</v>
       </c>
       <c r="K3" t="n">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="L3" t="n">
-        <v>999.1</v>
+        <v>975.4</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>860</v>
+        <v>823</v>
       </c>
       <c r="C4" t="n">
-        <v>1064</v>
+        <v>871</v>
       </c>
       <c r="D4" t="n">
-        <v>1154</v>
+        <v>979</v>
       </c>
       <c r="E4" t="n">
-        <v>992</v>
+        <v>974</v>
       </c>
       <c r="F4" t="n">
-        <v>1091</v>
+        <v>991</v>
       </c>
       <c r="G4" t="n">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H4" t="n">
-        <v>977</v>
+        <v>883</v>
       </c>
       <c r="I4" t="n">
-        <v>920</v>
+        <v>1029</v>
       </c>
       <c r="J4" t="n">
-        <v>1038</v>
+        <v>859</v>
       </c>
       <c r="K4" t="n">
-        <v>923</v>
+        <v>1068</v>
       </c>
       <c r="L4" t="n">
-        <v>994.2</v>
+        <v>940.1</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>1043</v>
+        <v>890</v>
       </c>
       <c r="C5" t="n">
-        <v>1035</v>
+        <v>844</v>
       </c>
       <c r="D5" t="n">
-        <v>1050</v>
+        <v>869</v>
       </c>
       <c r="E5" t="n">
-        <v>1006</v>
+        <v>995</v>
       </c>
       <c r="F5" t="n">
-        <v>1054</v>
+        <v>916</v>
       </c>
       <c r="G5" t="n">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="H5" t="n">
-        <v>1275</v>
+        <v>947</v>
       </c>
       <c r="I5" t="n">
-        <v>996</v>
+        <v>868</v>
       </c>
       <c r="J5" t="n">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="K5" t="n">
-        <v>886</v>
+        <v>961</v>
       </c>
       <c r="L5" t="n">
-        <v>1013.1</v>
+        <v>907.4</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>1022</v>
+        <v>887</v>
       </c>
       <c r="C6" t="n">
-        <v>1038</v>
+        <v>773</v>
       </c>
       <c r="D6" t="n">
-        <v>826</v>
+        <v>863</v>
       </c>
       <c r="E6" t="n">
-        <v>1057</v>
+        <v>827</v>
       </c>
       <c r="F6" t="n">
-        <v>889</v>
+        <v>798</v>
       </c>
       <c r="G6" t="n">
-        <v>1077</v>
+        <v>966</v>
       </c>
       <c r="H6" t="n">
-        <v>1054</v>
+        <v>992</v>
       </c>
       <c r="I6" t="n">
-        <v>1198</v>
+        <v>966</v>
       </c>
       <c r="J6" t="n">
-        <v>1229</v>
+        <v>793</v>
       </c>
       <c r="K6" t="n">
-        <v>963</v>
+        <v>907</v>
       </c>
       <c r="L6" t="n">
-        <v>1035.3</v>
+        <v>877.2</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>1018</v>
+        <v>927</v>
       </c>
       <c r="C7" t="n">
-        <v>909</v>
+        <v>870</v>
       </c>
       <c r="D7" t="n">
-        <v>977</v>
+        <v>925</v>
       </c>
       <c r="E7" t="n">
-        <v>1076</v>
+        <v>934</v>
       </c>
       <c r="F7" t="n">
-        <v>1201</v>
+        <v>1062</v>
       </c>
       <c r="G7" t="n">
-        <v>1163</v>
+        <v>978</v>
       </c>
       <c r="H7" t="n">
-        <v>1145</v>
+        <v>957</v>
       </c>
       <c r="I7" t="n">
-        <v>1091</v>
+        <v>881</v>
       </c>
       <c r="J7" t="n">
-        <v>999</v>
+        <v>900</v>
       </c>
       <c r="K7" t="n">
-        <v>890</v>
+        <v>968</v>
       </c>
       <c r="L7" t="n">
-        <v>1046.9</v>
+        <v>940.2</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C8" t="n">
-        <v>1003</v>
+        <v>899</v>
       </c>
       <c r="D8" t="n">
-        <v>928</v>
+        <v>1028</v>
       </c>
       <c r="E8" t="n">
-        <v>927</v>
+        <v>955</v>
       </c>
       <c r="F8" t="n">
-        <v>903</v>
+        <v>890</v>
       </c>
       <c r="G8" t="n">
-        <v>965</v>
+        <v>949</v>
       </c>
       <c r="H8" t="n">
-        <v>873</v>
+        <v>1028</v>
       </c>
       <c r="I8" t="n">
-        <v>963</v>
+        <v>1037</v>
       </c>
       <c r="J8" t="n">
-        <v>1151</v>
+        <v>976</v>
       </c>
       <c r="K8" t="n">
-        <v>1015</v>
+        <v>1036</v>
       </c>
       <c r="L8" t="n">
-        <v>959.5</v>
+        <v>966.7</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>1030</v>
+        <v>1085</v>
       </c>
       <c r="C9" t="n">
-        <v>971</v>
+        <v>961</v>
       </c>
       <c r="D9" t="n">
-        <v>1050</v>
+        <v>909</v>
       </c>
       <c r="E9" t="n">
-        <v>1068</v>
+        <v>837</v>
       </c>
       <c r="F9" t="n">
-        <v>1024</v>
+        <v>1044</v>
       </c>
       <c r="G9" t="n">
-        <v>858</v>
+        <v>1043</v>
       </c>
       <c r="H9" t="n">
-        <v>1117</v>
+        <v>1138</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>896</v>
       </c>
       <c r="J9" t="n">
-        <v>952</v>
+        <v>943</v>
       </c>
       <c r="K9" t="n">
-        <v>1111</v>
+        <v>933</v>
       </c>
       <c r="L9" t="n">
-        <v>1018.1</v>
+        <v>978.9</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>922</v>
+        <v>1032</v>
       </c>
       <c r="C10" t="n">
-        <v>904</v>
+        <v>924</v>
       </c>
       <c r="D10" t="n">
-        <v>885</v>
+        <v>801</v>
       </c>
       <c r="E10" t="n">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="F10" t="n">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="G10" t="n">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="H10" t="n">
-        <v>982</v>
+        <v>723</v>
       </c>
       <c r="I10" t="n">
-        <v>927</v>
+        <v>770</v>
       </c>
       <c r="J10" t="n">
-        <v>913</v>
+        <v>855</v>
       </c>
       <c r="K10" t="n">
-        <v>980</v>
+        <v>915</v>
       </c>
       <c r="L10" t="n">
-        <v>934.3</v>
+        <v>885.6</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1044</v>
+        <v>939</v>
       </c>
       <c r="C11" t="n">
-        <v>995</v>
+        <v>1057</v>
       </c>
       <c r="D11" t="n">
-        <v>1175</v>
+        <v>836</v>
       </c>
       <c r="E11" t="n">
-        <v>1035</v>
+        <v>823</v>
       </c>
       <c r="F11" t="n">
-        <v>936</v>
+        <v>985</v>
       </c>
       <c r="G11" t="n">
-        <v>903</v>
+        <v>756</v>
       </c>
       <c r="H11" t="n">
-        <v>979</v>
+        <v>899</v>
       </c>
       <c r="I11" t="n">
-        <v>1287</v>
+        <v>896</v>
       </c>
       <c r="J11" t="n">
-        <v>857</v>
+        <v>915</v>
       </c>
       <c r="K11" t="n">
-        <v>1005</v>
+        <v>1037</v>
       </c>
       <c r="L11" t="n">
-        <v>1021.6</v>
+        <v>914.3</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1155</v>
+        <v>830</v>
       </c>
       <c r="C12" t="n">
-        <v>941</v>
+        <v>895</v>
       </c>
       <c r="D12" t="n">
-        <v>1104</v>
+        <v>917</v>
       </c>
       <c r="E12" t="n">
-        <v>1035</v>
+        <v>926</v>
       </c>
       <c r="F12" t="n">
-        <v>956</v>
+        <v>946</v>
       </c>
       <c r="G12" t="n">
-        <v>989</v>
+        <v>913</v>
       </c>
       <c r="H12" t="n">
-        <v>982</v>
+        <v>811</v>
       </c>
       <c r="I12" t="n">
-        <v>978</v>
+        <v>882</v>
       </c>
       <c r="J12" t="n">
-        <v>1177</v>
+        <v>963</v>
       </c>
       <c r="K12" t="n">
-        <v>1044</v>
+        <v>898</v>
       </c>
       <c r="L12" t="n">
-        <v>1036.1</v>
+        <v>898.1</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>1002</v>
+        <v>1062</v>
       </c>
       <c r="C13" t="n">
-        <v>997</v>
+        <v>841</v>
       </c>
       <c r="D13" t="n">
-        <v>924</v>
+        <v>822</v>
       </c>
       <c r="E13" t="n">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="F13" t="n">
-        <v>1023</v>
+        <v>751</v>
       </c>
       <c r="G13" t="n">
-        <v>895</v>
+        <v>982</v>
       </c>
       <c r="H13" t="n">
-        <v>1054</v>
+        <v>990</v>
       </c>
       <c r="I13" t="n">
-        <v>1067</v>
+        <v>933</v>
       </c>
       <c r="J13" t="n">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="K13" t="n">
-        <v>968</v>
+        <v>1004</v>
       </c>
       <c r="L13" t="n">
-        <v>982.6</v>
+        <v>927.6</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
+        <v>1104</v>
+      </c>
+      <c r="C14" t="n">
+        <v>901</v>
+      </c>
+      <c r="D14" t="n">
+        <v>941</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1016</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1023</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1072</v>
+      </c>
+      <c r="H14" t="n">
         <v>985</v>
       </c>
-      <c r="C14" t="n">
-        <v>969</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1087</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1163</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1073</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1004</v>
-      </c>
-      <c r="H14" t="n">
-        <v>925</v>
-      </c>
       <c r="I14" t="n">
-        <v>1025</v>
+        <v>962</v>
       </c>
       <c r="J14" t="n">
-        <v>1130</v>
+        <v>964</v>
       </c>
       <c r="K14" t="n">
-        <v>1042</v>
+        <v>841</v>
       </c>
       <c r="L14" t="n">
-        <v>1040.3</v>
+        <v>980.9</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>1369</v>
+        <v>1038</v>
       </c>
       <c r="C15" t="n">
-        <v>976</v>
+        <v>1051</v>
       </c>
       <c r="D15" t="n">
-        <v>980</v>
+        <v>989</v>
       </c>
       <c r="E15" t="n">
-        <v>1180</v>
+        <v>1027</v>
       </c>
       <c r="F15" t="n">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="G15" t="n">
-        <v>1224</v>
+        <v>877</v>
       </c>
       <c r="H15" t="n">
-        <v>856</v>
+        <v>892</v>
       </c>
       <c r="I15" t="n">
-        <v>1099</v>
+        <v>1108</v>
       </c>
       <c r="J15" t="n">
-        <v>936</v>
+        <v>1069</v>
       </c>
       <c r="K15" t="n">
-        <v>1273</v>
+        <v>940</v>
       </c>
       <c r="L15" t="n">
-        <v>1079</v>
+        <v>989.5</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>1038</v>
+        <v>934</v>
       </c>
       <c r="C16" t="n">
-        <v>988</v>
+        <v>907</v>
       </c>
       <c r="D16" t="n">
-        <v>1073</v>
+        <v>1110</v>
       </c>
       <c r="E16" t="n">
-        <v>1029</v>
+        <v>891</v>
       </c>
       <c r="F16" t="n">
-        <v>998</v>
+        <v>865</v>
       </c>
       <c r="G16" t="n">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H16" t="n">
-        <v>1054</v>
+        <v>964</v>
       </c>
       <c r="I16" t="n">
-        <v>920</v>
+        <v>911</v>
       </c>
       <c r="J16" t="n">
-        <v>1202</v>
+        <v>885</v>
       </c>
       <c r="K16" t="n">
-        <v>1038</v>
+        <v>977</v>
       </c>
       <c r="L16" t="n">
-        <v>1020.5</v>
+        <v>930.8</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C17" t="n">
-        <v>807</v>
+        <v>875</v>
       </c>
       <c r="D17" t="n">
-        <v>1074</v>
+        <v>751</v>
       </c>
       <c r="E17" t="n">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="F17" t="n">
-        <v>911</v>
+        <v>982</v>
       </c>
       <c r="G17" t="n">
-        <v>1030</v>
+        <v>888</v>
       </c>
       <c r="H17" t="n">
-        <v>1004</v>
+        <v>905</v>
       </c>
       <c r="I17" t="n">
-        <v>1053</v>
+        <v>895</v>
       </c>
       <c r="J17" t="n">
-        <v>1103</v>
+        <v>840</v>
       </c>
       <c r="K17" t="n">
-        <v>822</v>
+        <v>790</v>
       </c>
       <c r="L17" t="n">
-        <v>944.6</v>
+        <v>857.4</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>1056</v>
+        <v>976</v>
       </c>
       <c r="C18" t="n">
-        <v>1016</v>
+        <v>982</v>
       </c>
       <c r="D18" t="n">
-        <v>1172</v>
+        <v>1090</v>
       </c>
       <c r="E18" t="n">
-        <v>981</v>
+        <v>900</v>
       </c>
       <c r="F18" t="n">
-        <v>1058</v>
+        <v>1034</v>
       </c>
       <c r="G18" t="n">
-        <v>1104</v>
+        <v>1031</v>
       </c>
       <c r="H18" t="n">
-        <v>1060</v>
+        <v>1022</v>
       </c>
       <c r="I18" t="n">
-        <v>1177</v>
+        <v>1110</v>
       </c>
       <c r="J18" t="n">
-        <v>1185</v>
+        <v>863</v>
       </c>
       <c r="K18" t="n">
-        <v>1193</v>
+        <v>1038</v>
       </c>
       <c r="L18" t="n">
-        <v>1100.2</v>
+        <v>1004.6</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>944</v>
+        <v>743</v>
       </c>
       <c r="C19" t="n">
-        <v>870</v>
+        <v>797</v>
       </c>
       <c r="D19" t="n">
-        <v>927</v>
+        <v>848</v>
       </c>
       <c r="E19" t="n">
-        <v>1023</v>
+        <v>788</v>
       </c>
       <c r="F19" t="n">
-        <v>1049</v>
+        <v>1035</v>
       </c>
       <c r="G19" t="n">
-        <v>994</v>
+        <v>739</v>
       </c>
       <c r="H19" t="n">
-        <v>1157</v>
+        <v>780</v>
       </c>
       <c r="I19" t="n">
-        <v>948</v>
+        <v>898</v>
       </c>
       <c r="J19" t="n">
-        <v>812</v>
+        <v>793</v>
       </c>
       <c r="K19" t="n">
-        <v>840</v>
+        <v>921</v>
       </c>
       <c r="L19" t="n">
-        <v>956.4</v>
+        <v>834.2</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>931</v>
+        <v>1190</v>
       </c>
       <c r="C20" t="n">
-        <v>923</v>
+        <v>914</v>
       </c>
       <c r="D20" t="n">
-        <v>965</v>
+        <v>915</v>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>735</v>
       </c>
       <c r="F20" t="n">
-        <v>1012</v>
+        <v>869</v>
       </c>
       <c r="G20" t="n">
-        <v>889</v>
+        <v>787</v>
       </c>
       <c r="H20" t="n">
-        <v>888</v>
+        <v>962</v>
       </c>
       <c r="I20" t="n">
-        <v>833</v>
+        <v>843</v>
       </c>
       <c r="J20" t="n">
-        <v>912</v>
+        <v>801</v>
       </c>
       <c r="K20" t="n">
-        <v>994</v>
+        <v>839</v>
       </c>
       <c r="L20" t="n">
-        <v>939.6</v>
+        <v>885.5</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>1266</v>
+        <v>887</v>
       </c>
       <c r="C21" t="n">
-        <v>1244</v>
+        <v>973</v>
       </c>
       <c r="D21" t="n">
-        <v>951</v>
+        <v>1115</v>
       </c>
       <c r="E21" t="n">
-        <v>1184</v>
+        <v>1155</v>
       </c>
       <c r="F21" t="n">
-        <v>989</v>
+        <v>1109</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>972</v>
       </c>
       <c r="H21" t="n">
-        <v>942</v>
+        <v>895</v>
       </c>
       <c r="I21" t="n">
-        <v>1058</v>
+        <v>971</v>
       </c>
       <c r="J21" t="n">
-        <v>1047</v>
+        <v>814</v>
       </c>
       <c r="K21" t="n">
-        <v>1250</v>
+        <v>974</v>
       </c>
       <c r="L21" t="n">
-        <v>1093.1</v>
+        <v>986.5</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>1044</v>
+        <v>929</v>
       </c>
       <c r="C22" t="n">
-        <v>1045</v>
+        <v>881</v>
       </c>
       <c r="D22" t="n">
-        <v>1031</v>
+        <v>894</v>
       </c>
       <c r="E22" t="n">
-        <v>1069</v>
+        <v>1062</v>
       </c>
       <c r="F22" t="n">
-        <v>1158</v>
+        <v>1002</v>
       </c>
       <c r="G22" t="n">
-        <v>891</v>
+        <v>987</v>
       </c>
       <c r="H22" t="n">
-        <v>849</v>
+        <v>968</v>
       </c>
       <c r="I22" t="n">
-        <v>940</v>
+        <v>893</v>
       </c>
       <c r="J22" t="n">
-        <v>785</v>
+        <v>993</v>
       </c>
       <c r="K22" t="n">
-        <v>1018</v>
+        <v>945</v>
       </c>
       <c r="L22" t="n">
-        <v>983</v>
+        <v>955.4</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1039</v>
+        <v>926</v>
       </c>
       <c r="C23" t="n">
-        <v>1030</v>
+        <v>962</v>
       </c>
       <c r="D23" t="n">
-        <v>961</v>
+        <v>872</v>
       </c>
       <c r="E23" t="n">
-        <v>1063</v>
+        <v>876</v>
       </c>
       <c r="F23" t="n">
-        <v>1033</v>
+        <v>959</v>
       </c>
       <c r="G23" t="n">
-        <v>994</v>
+        <v>937</v>
       </c>
       <c r="H23" t="n">
-        <v>1184</v>
+        <v>814</v>
       </c>
       <c r="I23" t="n">
-        <v>906</v>
+        <v>1010</v>
       </c>
       <c r="J23" t="n">
-        <v>1151</v>
+        <v>954</v>
       </c>
       <c r="K23" t="n">
-        <v>982</v>
+        <v>955</v>
       </c>
       <c r="L23" t="n">
-        <v>1034.3</v>
+        <v>926.5</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>1120</v>
+        <v>993</v>
       </c>
       <c r="C24" t="n">
-        <v>1065</v>
+        <v>1007</v>
       </c>
       <c r="D24" t="n">
-        <v>978</v>
+        <v>882</v>
       </c>
       <c r="E24" t="n">
-        <v>1017</v>
+        <v>957</v>
       </c>
       <c r="F24" t="n">
-        <v>1001</v>
+        <v>851</v>
       </c>
       <c r="G24" t="n">
-        <v>868</v>
+        <v>1012</v>
       </c>
       <c r="H24" t="n">
-        <v>1267</v>
+        <v>958</v>
       </c>
       <c r="I24" t="n">
-        <v>943</v>
+        <v>893</v>
       </c>
       <c r="J24" t="n">
-        <v>1014</v>
+        <v>855</v>
       </c>
       <c r="K24" t="n">
-        <v>1018</v>
+        <v>988</v>
       </c>
       <c r="L24" t="n">
-        <v>1029.1</v>
+        <v>939.6</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>1003</v>
+        <v>1061</v>
       </c>
       <c r="C25" t="n">
-        <v>953</v>
+        <v>976</v>
       </c>
       <c r="D25" t="n">
-        <v>918</v>
+        <v>929</v>
       </c>
       <c r="E25" t="n">
-        <v>1132</v>
+        <v>954</v>
       </c>
       <c r="F25" t="n">
-        <v>1047</v>
+        <v>945</v>
       </c>
       <c r="G25" t="n">
-        <v>903</v>
+        <v>929</v>
       </c>
       <c r="H25" t="n">
-        <v>1061</v>
+        <v>922</v>
       </c>
       <c r="I25" t="n">
-        <v>1146</v>
+        <v>941</v>
       </c>
       <c r="J25" t="n">
-        <v>974</v>
+        <v>942</v>
       </c>
       <c r="K25" t="n">
-        <v>1017</v>
+        <v>916</v>
       </c>
       <c r="L25" t="n">
-        <v>1015.4</v>
+        <v>951.5</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>1126</v>
+        <v>1059</v>
       </c>
       <c r="C26" t="n">
-        <v>1025</v>
+        <v>951</v>
       </c>
       <c r="D26" t="n">
-        <v>1163</v>
+        <v>1139</v>
       </c>
       <c r="E26" t="n">
-        <v>1294</v>
+        <v>1058</v>
       </c>
       <c r="F26" t="n">
-        <v>1181</v>
+        <v>930</v>
       </c>
       <c r="G26" t="n">
-        <v>901</v>
+        <v>1039</v>
       </c>
       <c r="H26" t="n">
-        <v>1106</v>
+        <v>968</v>
       </c>
       <c r="I26" t="n">
-        <v>1003</v>
+        <v>922</v>
       </c>
       <c r="J26" t="n">
-        <v>1178</v>
+        <v>1024</v>
       </c>
       <c r="K26" t="n">
-        <v>1225</v>
+        <v>1154</v>
       </c>
       <c r="L26" t="n">
-        <v>1120.2</v>
+        <v>1024.4</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1122</v>
+        <v>1149</v>
       </c>
       <c r="C27" t="n">
-        <v>1013</v>
+        <v>1027</v>
       </c>
       <c r="D27" t="n">
-        <v>1108</v>
+        <v>1094</v>
       </c>
       <c r="E27" t="n">
-        <v>1166</v>
+        <v>1043</v>
       </c>
       <c r="F27" t="n">
-        <v>1143</v>
+        <v>1124</v>
       </c>
       <c r="G27" t="n">
-        <v>1248</v>
+        <v>1040</v>
       </c>
       <c r="H27" t="n">
-        <v>1303</v>
+        <v>959</v>
       </c>
       <c r="I27" t="n">
-        <v>1147</v>
+        <v>1044</v>
       </c>
       <c r="J27" t="n">
-        <v>1056</v>
+        <v>922</v>
       </c>
       <c r="K27" t="n">
-        <v>1157</v>
+        <v>912</v>
       </c>
       <c r="L27" t="n">
-        <v>1146.3</v>
+        <v>1031.4</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>785</v>
+        <v>990</v>
       </c>
       <c r="C28" t="n">
-        <v>1058</v>
+        <v>899</v>
       </c>
       <c r="D28" t="n">
-        <v>992</v>
+        <v>863</v>
       </c>
       <c r="E28" t="n">
-        <v>1023</v>
+        <v>824</v>
       </c>
       <c r="F28" t="n">
-        <v>1008</v>
+        <v>783</v>
       </c>
       <c r="G28" t="n">
-        <v>948</v>
+        <v>966</v>
       </c>
       <c r="H28" t="n">
-        <v>919</v>
+        <v>831</v>
       </c>
       <c r="I28" t="n">
         <v>894</v>
       </c>
       <c r="J28" t="n">
-        <v>814</v>
+        <v>959</v>
       </c>
       <c r="K28" t="n">
-        <v>986</v>
+        <v>932</v>
       </c>
       <c r="L28" t="n">
-        <v>942.7</v>
+        <v>894.1</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>1102</v>
+        <v>878</v>
       </c>
       <c r="C29" t="n">
-        <v>1107</v>
+        <v>824</v>
       </c>
       <c r="D29" t="n">
-        <v>925</v>
+        <v>882</v>
       </c>
       <c r="E29" t="n">
-        <v>912</v>
+        <v>939</v>
       </c>
       <c r="F29" t="n">
-        <v>1002</v>
+        <v>823</v>
       </c>
       <c r="G29" t="n">
-        <v>1006</v>
+        <v>797</v>
       </c>
       <c r="H29" t="n">
-        <v>995</v>
+        <v>852</v>
       </c>
       <c r="I29" t="n">
-        <v>893</v>
+        <v>1030</v>
       </c>
       <c r="J29" t="n">
-        <v>859</v>
+        <v>960</v>
       </c>
       <c r="K29" t="n">
-        <v>1053</v>
+        <v>871</v>
       </c>
       <c r="L29" t="n">
-        <v>985.4</v>
+        <v>885.6</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>878</v>
+        <v>1058</v>
       </c>
       <c r="C30" t="n">
-        <v>1130</v>
+        <v>851</v>
       </c>
       <c r="D30" t="n">
-        <v>900</v>
+        <v>952</v>
       </c>
       <c r="E30" t="n">
-        <v>1102</v>
+        <v>830</v>
       </c>
       <c r="F30" t="n">
-        <v>1050</v>
+        <v>901</v>
       </c>
       <c r="G30" t="n">
-        <v>940</v>
+        <v>828</v>
       </c>
       <c r="H30" t="n">
-        <v>990</v>
+        <v>810</v>
       </c>
       <c r="I30" t="n">
-        <v>1040</v>
+        <v>929</v>
       </c>
       <c r="J30" t="n">
-        <v>912</v>
+        <v>1037</v>
       </c>
       <c r="K30" t="n">
-        <v>950</v>
+        <v>917</v>
       </c>
       <c r="L30" t="n">
-        <v>989.2</v>
+        <v>911.3</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1089</v>
+        <v>1028</v>
       </c>
       <c r="C31" t="n">
-        <v>823</v>
+        <v>910</v>
       </c>
       <c r="D31" t="n">
-        <v>916</v>
+        <v>1028</v>
       </c>
       <c r="E31" t="n">
-        <v>1041</v>
+        <v>980</v>
       </c>
       <c r="F31" t="n">
-        <v>947</v>
+        <v>993</v>
       </c>
       <c r="G31" t="n">
-        <v>888</v>
+        <v>1010</v>
       </c>
       <c r="H31" t="n">
-        <v>891</v>
+        <v>1078</v>
       </c>
       <c r="I31" t="n">
-        <v>1103</v>
+        <v>966</v>
       </c>
       <c r="J31" t="n">
-        <v>868</v>
+        <v>1007</v>
       </c>
       <c r="K31" t="n">
-        <v>956</v>
+        <v>877</v>
       </c>
       <c r="L31" t="n">
-        <v>952.2</v>
+        <v>987.7</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>1120</v>
+        <v>1171</v>
       </c>
       <c r="C32" t="n">
-        <v>1240</v>
+        <v>1105</v>
       </c>
       <c r="D32" t="n">
-        <v>958</v>
+        <v>1122</v>
       </c>
       <c r="E32" t="n">
-        <v>1330</v>
+        <v>1184</v>
       </c>
       <c r="F32" t="n">
-        <v>1063</v>
+        <v>993</v>
       </c>
       <c r="G32" t="n">
-        <v>1127</v>
+        <v>1077</v>
       </c>
       <c r="H32" t="n">
-        <v>1053</v>
+        <v>1126</v>
       </c>
       <c r="I32" t="n">
-        <v>1086</v>
+        <v>1099</v>
       </c>
       <c r="J32" t="n">
-        <v>1149</v>
+        <v>1095</v>
       </c>
       <c r="K32" t="n">
-        <v>1250</v>
+        <v>1126</v>
       </c>
       <c r="L32" t="n">
-        <v>1137.6</v>
+        <v>1109.8</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>902</v>
+        <v>871</v>
       </c>
       <c r="C33" t="n">
-        <v>1008</v>
+        <v>988</v>
       </c>
       <c r="D33" t="n">
-        <v>871</v>
+        <v>958</v>
       </c>
       <c r="E33" t="n">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="F33" t="n">
-        <v>828</v>
+        <v>906</v>
       </c>
       <c r="G33" t="n">
-        <v>962</v>
+        <v>895</v>
       </c>
       <c r="H33" t="n">
-        <v>1007</v>
+        <v>1020</v>
       </c>
       <c r="I33" t="n">
-        <v>933</v>
+        <v>906</v>
       </c>
       <c r="J33" t="n">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="K33" t="n">
-        <v>1165</v>
+        <v>965</v>
       </c>
       <c r="L33" t="n">
-        <v>949.6</v>
+        <v>934.7</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>1210</v>
+        <v>1002</v>
       </c>
       <c r="C34" t="n">
-        <v>978</v>
+        <v>1110</v>
       </c>
       <c r="D34" t="n">
-        <v>1313</v>
+        <v>977</v>
       </c>
       <c r="E34" t="n">
-        <v>1243</v>
+        <v>823</v>
       </c>
       <c r="F34" t="n">
-        <v>1078</v>
+        <v>1119</v>
       </c>
       <c r="G34" t="n">
-        <v>1025</v>
+        <v>824</v>
       </c>
       <c r="H34" t="n">
-        <v>1044</v>
+        <v>897</v>
       </c>
       <c r="I34" t="n">
-        <v>1279</v>
+        <v>1042</v>
       </c>
       <c r="J34" t="n">
-        <v>1010</v>
+        <v>1064</v>
       </c>
       <c r="K34" t="n">
-        <v>1189</v>
+        <v>930</v>
       </c>
       <c r="L34" t="n">
-        <v>1136.9</v>
+        <v>978.8</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>1254</v>
+        <v>926</v>
       </c>
       <c r="C35" t="n">
-        <v>1143</v>
+        <v>1062</v>
       </c>
       <c r="D35" t="n">
-        <v>1038</v>
+        <v>1092</v>
       </c>
       <c r="E35" t="n">
-        <v>1091</v>
+        <v>872</v>
       </c>
       <c r="F35" t="n">
-        <v>1068</v>
+        <v>914</v>
       </c>
       <c r="G35" t="n">
-        <v>1066</v>
+        <v>861</v>
       </c>
       <c r="H35" t="n">
-        <v>1025</v>
+        <v>981</v>
       </c>
       <c r="I35" t="n">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="J35" t="n">
-        <v>1037</v>
+        <v>1075</v>
       </c>
       <c r="K35" t="n">
-        <v>1205</v>
+        <v>1012</v>
       </c>
       <c r="L35" t="n">
-        <v>1096</v>
+        <v>982.2</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>944</v>
+        <v>864</v>
       </c>
       <c r="C36" t="n">
-        <v>1081</v>
+        <v>942</v>
       </c>
       <c r="D36" t="n">
-        <v>954</v>
+        <v>1012</v>
       </c>
       <c r="E36" t="n">
-        <v>901</v>
+        <v>987</v>
       </c>
       <c r="F36" t="n">
-        <v>1132</v>
+        <v>1108</v>
       </c>
       <c r="G36" t="n">
-        <v>914</v>
+        <v>961</v>
       </c>
       <c r="H36" t="n">
-        <v>1038</v>
+        <v>1117</v>
       </c>
       <c r="I36" t="n">
-        <v>951</v>
+        <v>1037</v>
       </c>
       <c r="J36" t="n">
-        <v>1177</v>
+        <v>898</v>
       </c>
       <c r="K36" t="n">
-        <v>1023</v>
+        <v>950</v>
       </c>
       <c r="L36" t="n">
-        <v>1011.5</v>
+        <v>987.6</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>1166</v>
+        <v>1034</v>
       </c>
       <c r="C37" t="n">
-        <v>1186</v>
+        <v>850</v>
       </c>
       <c r="D37" t="n">
-        <v>934</v>
+        <v>867</v>
       </c>
       <c r="E37" t="n">
-        <v>1073</v>
+        <v>922</v>
       </c>
       <c r="F37" t="n">
-        <v>981</v>
+        <v>904</v>
       </c>
       <c r="G37" t="n">
-        <v>1062</v>
+        <v>927</v>
       </c>
       <c r="H37" t="n">
-        <v>1060</v>
+        <v>943</v>
       </c>
       <c r="I37" t="n">
-        <v>1208</v>
+        <v>857</v>
       </c>
       <c r="J37" t="n">
-        <v>1120</v>
+        <v>884</v>
       </c>
       <c r="K37" t="n">
-        <v>961</v>
+        <v>1009</v>
       </c>
       <c r="L37" t="n">
-        <v>1075.1</v>
+        <v>919.7</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>867</v>
+        <v>942</v>
       </c>
       <c r="C38" t="n">
-        <v>958</v>
+        <v>911</v>
       </c>
       <c r="D38" t="n">
-        <v>982</v>
+        <v>841</v>
       </c>
       <c r="E38" t="n">
-        <v>925</v>
+        <v>817</v>
       </c>
       <c r="F38" t="n">
-        <v>973</v>
+        <v>767</v>
       </c>
       <c r="G38" t="n">
-        <v>910</v>
+        <v>841</v>
       </c>
       <c r="H38" t="n">
-        <v>911</v>
+        <v>873</v>
       </c>
       <c r="I38" t="n">
-        <v>896</v>
+        <v>796</v>
       </c>
       <c r="J38" t="n">
-        <v>972</v>
+        <v>909</v>
       </c>
       <c r="K38" t="n">
-        <v>936</v>
+        <v>819</v>
       </c>
       <c r="L38" t="n">
-        <v>933</v>
+        <v>851.6</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>897</v>
+        <v>861</v>
       </c>
       <c r="C39" t="n">
-        <v>999</v>
+        <v>1004</v>
       </c>
       <c r="D39" t="n">
-        <v>816</v>
+        <v>990</v>
       </c>
       <c r="E39" t="n">
+        <v>886</v>
+      </c>
+      <c r="F39" t="n">
+        <v>846</v>
+      </c>
+      <c r="G39" t="n">
+        <v>950</v>
+      </c>
+      <c r="H39" t="n">
         <v>925</v>
       </c>
-      <c r="F39" t="n">
-        <v>864</v>
-      </c>
-      <c r="G39" t="n">
-        <v>820</v>
-      </c>
-      <c r="H39" t="n">
-        <v>888</v>
-      </c>
       <c r="I39" t="n">
-        <v>832</v>
+        <v>1008</v>
       </c>
       <c r="J39" t="n">
-        <v>1114</v>
+        <v>1030</v>
       </c>
       <c r="K39" t="n">
-        <v>948</v>
+        <v>871</v>
       </c>
       <c r="L39" t="n">
-        <v>910.3</v>
+        <v>937.1</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>1070</v>
+        <v>871</v>
       </c>
       <c r="C40" t="n">
-        <v>1069</v>
+        <v>839</v>
       </c>
       <c r="D40" t="n">
-        <v>1121</v>
+        <v>800</v>
       </c>
       <c r="E40" t="n">
-        <v>918</v>
+        <v>856</v>
       </c>
       <c r="F40" t="n">
-        <v>995</v>
+        <v>964</v>
       </c>
       <c r="G40" t="n">
-        <v>953</v>
+        <v>970</v>
       </c>
       <c r="H40" t="n">
-        <v>962</v>
+        <v>889</v>
       </c>
       <c r="I40" t="n">
-        <v>1044</v>
+        <v>867</v>
       </c>
       <c r="J40" t="n">
-        <v>853</v>
+        <v>920</v>
       </c>
       <c r="K40" t="n">
-        <v>1151</v>
+        <v>1007</v>
       </c>
       <c r="L40" t="n">
-        <v>1013.6</v>
+        <v>898.3</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>870</v>
+        <v>911</v>
       </c>
       <c r="C41" t="n">
-        <v>864</v>
+        <v>957</v>
       </c>
       <c r="D41" t="n">
-        <v>872</v>
+        <v>832</v>
       </c>
       <c r="E41" t="n">
-        <v>1056</v>
+        <v>795</v>
       </c>
       <c r="F41" t="n">
-        <v>915</v>
+        <v>947</v>
       </c>
       <c r="G41" t="n">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="H41" t="n">
-        <v>881</v>
+        <v>771</v>
       </c>
       <c r="I41" t="n">
-        <v>903</v>
+        <v>921</v>
       </c>
       <c r="J41" t="n">
-        <v>1125</v>
+        <v>913</v>
       </c>
       <c r="K41" t="n">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="L41" t="n">
-        <v>932.5</v>
+        <v>889.2</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>782</v>
+        <v>949</v>
       </c>
       <c r="C42" t="n">
-        <v>937</v>
+        <v>846</v>
       </c>
       <c r="D42" t="n">
-        <v>1004</v>
+        <v>857</v>
       </c>
       <c r="E42" t="n">
-        <v>858</v>
+        <v>913</v>
       </c>
       <c r="F42" t="n">
-        <v>882</v>
+        <v>809</v>
       </c>
       <c r="G42" t="n">
-        <v>1048</v>
+        <v>849</v>
       </c>
       <c r="H42" t="n">
-        <v>817</v>
+        <v>804</v>
       </c>
       <c r="I42" t="n">
-        <v>983</v>
+        <v>946</v>
       </c>
       <c r="J42" t="n">
-        <v>899</v>
+        <v>944</v>
       </c>
       <c r="K42" t="n">
-        <v>973</v>
+        <v>854</v>
       </c>
       <c r="L42" t="n">
-        <v>918.3</v>
+        <v>877.1</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="C43" t="n">
-        <v>949</v>
+        <v>862</v>
       </c>
       <c r="D43" t="n">
-        <v>1010</v>
+        <v>771</v>
       </c>
       <c r="E43" t="n">
-        <v>841</v>
+        <v>872</v>
       </c>
       <c r="F43" t="n">
-        <v>896</v>
+        <v>808</v>
       </c>
       <c r="G43" t="n">
-        <v>876</v>
+        <v>917</v>
       </c>
       <c r="H43" t="n">
-        <v>844</v>
+        <v>860</v>
       </c>
       <c r="I43" t="n">
-        <v>993</v>
+        <v>879</v>
       </c>
       <c r="J43" t="n">
-        <v>937</v>
+        <v>802</v>
       </c>
       <c r="K43" t="n">
-        <v>822</v>
+        <v>906</v>
       </c>
       <c r="L43" t="n">
-        <v>911.1</v>
+        <v>861.8</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>1010</v>
+        <v>748</v>
       </c>
       <c r="C44" t="n">
-        <v>1033</v>
+        <v>871</v>
       </c>
       <c r="D44" t="n">
-        <v>822</v>
+        <v>749</v>
       </c>
       <c r="E44" t="n">
-        <v>1016</v>
+        <v>787</v>
       </c>
       <c r="F44" t="n">
-        <v>961</v>
+        <v>847</v>
       </c>
       <c r="G44" t="n">
-        <v>971</v>
+        <v>756</v>
       </c>
       <c r="H44" t="n">
-        <v>895</v>
+        <v>840</v>
       </c>
       <c r="I44" t="n">
-        <v>1121</v>
+        <v>896</v>
       </c>
       <c r="J44" t="n">
-        <v>891</v>
+        <v>880</v>
       </c>
       <c r="K44" t="n">
-        <v>883</v>
+        <v>865</v>
       </c>
       <c r="L44" t="n">
-        <v>960.3</v>
+        <v>823.9</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1140</v>
+        <v>1035</v>
       </c>
       <c r="C45" t="n">
-        <v>1095</v>
+        <v>1124</v>
       </c>
       <c r="D45" t="n">
-        <v>1114</v>
+        <v>937</v>
       </c>
       <c r="E45" t="n">
-        <v>1042</v>
+        <v>1019</v>
       </c>
       <c r="F45" t="n">
-        <v>1121</v>
+        <v>1084</v>
       </c>
       <c r="G45" t="n">
-        <v>1130</v>
+        <v>1004</v>
       </c>
       <c r="H45" t="n">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="I45" t="n">
-        <v>1020</v>
+        <v>1191</v>
       </c>
       <c r="J45" t="n">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="K45" t="n">
-        <v>1161</v>
+        <v>1040</v>
       </c>
       <c r="L45" t="n">
-        <v>1091.7</v>
+        <v>1052.9</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>950</v>
+        <v>882</v>
       </c>
       <c r="C46" t="n">
-        <v>1242</v>
+        <v>1032</v>
       </c>
       <c r="D46" t="n">
-        <v>912</v>
+        <v>818</v>
       </c>
       <c r="E46" t="n">
-        <v>743</v>
+        <v>997</v>
       </c>
       <c r="F46" t="n">
-        <v>1131</v>
+        <v>882</v>
       </c>
       <c r="G46" t="n">
-        <v>939</v>
+        <v>958</v>
       </c>
       <c r="H46" t="n">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="I46" t="n">
-        <v>1011</v>
+        <v>938</v>
       </c>
       <c r="J46" t="n">
-        <v>912</v>
+        <v>871</v>
       </c>
       <c r="K46" t="n">
-        <v>962</v>
+        <v>1083</v>
       </c>
       <c r="L46" t="n">
-        <v>974.2</v>
+        <v>940.2</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
+        <v>1096</v>
+      </c>
+      <c r="C47" t="n">
+        <v>936</v>
+      </c>
+      <c r="D47" t="n">
+        <v>934</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1001</v>
+      </c>
+      <c r="F47" t="n">
         <v>1090</v>
       </c>
-      <c r="C47" t="n">
-        <v>1195</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1222</v>
-      </c>
-      <c r="E47" t="n">
-        <v>1030</v>
-      </c>
-      <c r="F47" t="n">
-        <v>1305</v>
-      </c>
       <c r="G47" t="n">
-        <v>1201</v>
+        <v>1146</v>
       </c>
       <c r="H47" t="n">
-        <v>990</v>
+        <v>1068</v>
       </c>
       <c r="I47" t="n">
-        <v>1150</v>
+        <v>1018</v>
       </c>
       <c r="J47" t="n">
-        <v>1061</v>
+        <v>966</v>
       </c>
       <c r="K47" t="n">
-        <v>1183</v>
+        <v>916</v>
       </c>
       <c r="L47" t="n">
-        <v>1142.7</v>
+        <v>1017.1</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>862</v>
+        <v>709</v>
       </c>
       <c r="C48" t="n">
-        <v>993</v>
+        <v>767</v>
       </c>
       <c r="D48" t="n">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="E48" t="n">
-        <v>763</v>
+        <v>852</v>
       </c>
       <c r="F48" t="n">
-        <v>951</v>
+        <v>900</v>
       </c>
       <c r="G48" t="n">
-        <v>1152</v>
+        <v>822</v>
       </c>
       <c r="H48" t="n">
-        <v>905</v>
+        <v>821</v>
       </c>
       <c r="I48" t="n">
-        <v>1018</v>
+        <v>950</v>
       </c>
       <c r="J48" t="n">
-        <v>864</v>
+        <v>782</v>
       </c>
       <c r="K48" t="n">
-        <v>792</v>
+        <v>743</v>
       </c>
       <c r="L48" t="n">
-        <v>908.6</v>
+        <v>812.4</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>1040</v>
+        <v>974</v>
       </c>
       <c r="C49" t="n">
-        <v>906</v>
+        <v>976</v>
       </c>
       <c r="D49" t="n">
-        <v>953</v>
+        <v>1140</v>
       </c>
       <c r="E49" t="n">
-        <v>1174</v>
+        <v>949</v>
       </c>
       <c r="F49" t="n">
-        <v>1162</v>
+        <v>1073</v>
       </c>
       <c r="G49" t="n">
-        <v>924</v>
+        <v>994</v>
       </c>
       <c r="H49" t="n">
-        <v>934</v>
+        <v>1004</v>
       </c>
       <c r="I49" t="n">
-        <v>925</v>
+        <v>1042</v>
       </c>
       <c r="J49" t="n">
-        <v>868</v>
+        <v>956</v>
       </c>
       <c r="K49" t="n">
-        <v>972</v>
+        <v>881</v>
       </c>
       <c r="L49" t="n">
-        <v>985.8</v>
+        <v>998.9</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>874</v>
+        <v>965</v>
       </c>
       <c r="C50" t="n">
-        <v>880</v>
+        <v>966</v>
       </c>
       <c r="D50" t="n">
-        <v>1112</v>
+        <v>926</v>
       </c>
       <c r="E50" t="n">
-        <v>1008</v>
+        <v>1048</v>
       </c>
       <c r="F50" t="n">
-        <v>975</v>
+        <v>942</v>
       </c>
       <c r="G50" t="n">
-        <v>1051</v>
+        <v>952</v>
       </c>
       <c r="H50" t="n">
-        <v>1076</v>
+        <v>928</v>
       </c>
       <c r="I50" t="n">
-        <v>970</v>
+        <v>1045</v>
       </c>
       <c r="J50" t="n">
-        <v>1171</v>
+        <v>907</v>
       </c>
       <c r="K50" t="n">
-        <v>869</v>
+        <v>947</v>
       </c>
       <c r="L50" t="n">
-        <v>998.6</v>
+        <v>962.6</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>1151</v>
+        <v>1000</v>
       </c>
       <c r="C51" t="n">
+        <v>1046</v>
+      </c>
+      <c r="D51" t="n">
+        <v>918</v>
+      </c>
+      <c r="E51" t="n">
+        <v>809</v>
+      </c>
+      <c r="F51" t="n">
+        <v>889</v>
+      </c>
+      <c r="G51" t="n">
+        <v>960</v>
+      </c>
+      <c r="H51" t="n">
         <v>949</v>
       </c>
-      <c r="D51" t="n">
-        <v>1017</v>
-      </c>
-      <c r="E51" t="n">
-        <v>882</v>
-      </c>
-      <c r="F51" t="n">
-        <v>1060</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1271</v>
-      </c>
-      <c r="H51" t="n">
-        <v>995</v>
-      </c>
       <c r="I51" t="n">
-        <v>916</v>
+        <v>832</v>
       </c>
       <c r="J51" t="n">
-        <v>902</v>
+        <v>832</v>
       </c>
       <c r="K51" t="n">
-        <v>933</v>
+        <v>901</v>
       </c>
       <c r="L51" t="n">
-        <v>1007.6</v>
+        <v>913.6</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1016.86</v>
+        <v>957.7</v>
       </c>
       <c r="C52" t="n">
-        <v>1014.32</v>
+        <v>936.72</v>
       </c>
       <c r="D52" t="n">
-        <v>1001.42</v>
+        <v>934.72</v>
       </c>
       <c r="E52" t="n">
-        <v>1020.48</v>
+        <v>922.88</v>
       </c>
       <c r="F52" t="n">
-        <v>1014.42</v>
+        <v>945.34</v>
       </c>
       <c r="G52" t="n">
-        <v>994.08</v>
+        <v>933.0599999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>1002.56</v>
+        <v>932.5</v>
       </c>
       <c r="I52" t="n">
-        <v>1016.48</v>
+        <v>952.46</v>
       </c>
       <c r="J52" t="n">
-        <v>999.16</v>
+        <v>928.9400000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>1020.12</v>
+        <v>943.8</v>
       </c>
       <c r="L52" t="n">
-        <v>1009.99</v>
+        <v>938.812</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>8.568264484405518</v>
+        <v>9.297962427139282</v>
       </c>
       <c r="C2" t="n">
-        <v>8.076156616210938</v>
+        <v>9.546410799026489</v>
       </c>
       <c r="D2" t="n">
-        <v>8.843694448471069</v>
+        <v>11.30013060569763</v>
       </c>
       <c r="E2" t="n">
-        <v>8.850813865661621</v>
+        <v>10.87441277503967</v>
       </c>
       <c r="F2" t="n">
-        <v>8.05915355682373</v>
+        <v>9.902348518371582</v>
       </c>
       <c r="G2" t="n">
-        <v>9.164770364761353</v>
+        <v>9.846519470214844</v>
       </c>
       <c r="H2" t="n">
-        <v>8.329646825790405</v>
+        <v>8.857218265533447</v>
       </c>
       <c r="I2" t="n">
-        <v>9.505357265472412</v>
+        <v>9.307791471481323</v>
       </c>
       <c r="J2" t="n">
-        <v>8.150044918060303</v>
+        <v>10.75750303268433</v>
       </c>
       <c r="K2" t="n">
-        <v>10.14166331291199</v>
+        <v>8.81865382194519</v>
       </c>
       <c r="L2" t="n">
-        <v>8.768956565856934</v>
+        <v>9.850895118713378</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>8.624410629272461</v>
+        <v>8.401284694671631</v>
       </c>
       <c r="C3" t="n">
-        <v>10.02405858039856</v>
+        <v>7.855454206466675</v>
       </c>
       <c r="D3" t="n">
-        <v>8.655624628067017</v>
+        <v>8.106597900390625</v>
       </c>
       <c r="E3" t="n">
-        <v>8.120419263839722</v>
+        <v>8.038296699523926</v>
       </c>
       <c r="F3" t="n">
-        <v>7.980723142623901</v>
+        <v>9.061217308044434</v>
       </c>
       <c r="G3" t="n">
-        <v>8.962850332260132</v>
+        <v>8.451765060424805</v>
       </c>
       <c r="H3" t="n">
-        <v>8.399992704391479</v>
+        <v>8.675758361816406</v>
       </c>
       <c r="I3" t="n">
-        <v>7.442545175552368</v>
+        <v>8.400544404983521</v>
       </c>
       <c r="J3" t="n">
-        <v>7.759900569915771</v>
+        <v>8.41106653213501</v>
       </c>
       <c r="K3" t="n">
-        <v>8.832559823989868</v>
+        <v>8.444834232330322</v>
       </c>
       <c r="L3" t="n">
-        <v>8.480308485031127</v>
+        <v>8.384681940078735</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>7.888206720352173</v>
+        <v>7.745209217071533</v>
       </c>
       <c r="C4" t="n">
-        <v>9.350841522216797</v>
+        <v>7.382197380065918</v>
       </c>
       <c r="D4" t="n">
-        <v>9.717632293701172</v>
+        <v>8.50480055809021</v>
       </c>
       <c r="E4" t="n">
-        <v>10.04866099357605</v>
+        <v>7.958205938339233</v>
       </c>
       <c r="F4" t="n">
-        <v>8.740153074264526</v>
+        <v>7.659024953842163</v>
       </c>
       <c r="G4" t="n">
-        <v>9.53893780708313</v>
+        <v>8.35728120803833</v>
       </c>
       <c r="H4" t="n">
-        <v>8.782580137252808</v>
+        <v>7.410723447799683</v>
       </c>
       <c r="I4" t="n">
-        <v>8.063674211502075</v>
+        <v>9.039109468460083</v>
       </c>
       <c r="J4" t="n">
-        <v>9.239198446273804</v>
+        <v>9.840832233428955</v>
       </c>
       <c r="K4" t="n">
-        <v>8.680485725402832</v>
+        <v>9.505623579025269</v>
       </c>
       <c r="L4" t="n">
-        <v>9.005037093162537</v>
+        <v>8.340300798416138</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>8.327800512313843</v>
+        <v>7.381651163101196</v>
       </c>
       <c r="C5" t="n">
-        <v>10.18273377418518</v>
+        <v>8.108945369720459</v>
       </c>
       <c r="D5" t="n">
-        <v>9.71365761756897</v>
+        <v>8.002570629119873</v>
       </c>
       <c r="E5" t="n">
-        <v>9.001159429550171</v>
+        <v>9.667191505432129</v>
       </c>
       <c r="F5" t="n">
-        <v>8.705506324768066</v>
+        <v>8.318587303161621</v>
       </c>
       <c r="G5" t="n">
-        <v>8.051343441009521</v>
+        <v>7.716564655303955</v>
       </c>
       <c r="H5" t="n">
-        <v>10.33758211135864</v>
+        <v>9.383012533187866</v>
       </c>
       <c r="I5" t="n">
-        <v>8.783103227615356</v>
+        <v>7.484983682632446</v>
       </c>
       <c r="J5" t="n">
-        <v>8.113252878189087</v>
+        <v>7.720354080200195</v>
       </c>
       <c r="K5" t="n">
-        <v>7.688122987747192</v>
+        <v>8.64970064163208</v>
       </c>
       <c r="L5" t="n">
-        <v>8.890426230430602</v>
+        <v>8.243356156349183</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>9.352102756500244</v>
+        <v>8.324737787246704</v>
       </c>
       <c r="C6" t="n">
-        <v>8.441574096679688</v>
+        <v>7.480994462966919</v>
       </c>
       <c r="D6" t="n">
-        <v>7.737651348114014</v>
+        <v>8.386323213577271</v>
       </c>
       <c r="E6" t="n">
-        <v>8.905929088592529</v>
+        <v>7.47412896156311</v>
       </c>
       <c r="F6" t="n">
-        <v>7.822906017303467</v>
+        <v>7.908902645111084</v>
       </c>
       <c r="G6" t="n">
-        <v>9.386373281478882</v>
+        <v>7.909761905670166</v>
       </c>
       <c r="H6" t="n">
-        <v>9.350225925445557</v>
+        <v>8.564718008041382</v>
       </c>
       <c r="I6" t="n">
-        <v>9.973835468292236</v>
+        <v>9.147382736206055</v>
       </c>
       <c r="J6" t="n">
-        <v>9.680401563644409</v>
+        <v>7.399251699447632</v>
       </c>
       <c r="K6" t="n">
-        <v>9.010055303573608</v>
+        <v>7.416801929473877</v>
       </c>
       <c r="L6" t="n">
-        <v>8.966105484962464</v>
+        <v>8.00130033493042</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>9.625638484954834</v>
+        <v>9.119611501693726</v>
       </c>
       <c r="C7" t="n">
-        <v>8.41902494430542</v>
+        <v>8.256339550018311</v>
       </c>
       <c r="D7" t="n">
-        <v>9.348613023757935</v>
+        <v>8.402722358703613</v>
       </c>
       <c r="E7" t="n">
-        <v>9.916548728942871</v>
+        <v>8.778525114059448</v>
       </c>
       <c r="F7" t="n">
-        <v>10.70699429512024</v>
+        <v>9.735963106155396</v>
       </c>
       <c r="G7" t="n">
-        <v>11.51482748985291</v>
+        <v>7.714987277984619</v>
       </c>
       <c r="H7" t="n">
-        <v>8.878434896469116</v>
+        <v>9.295515298843384</v>
       </c>
       <c r="I7" t="n">
-        <v>9.340049028396606</v>
+        <v>8.554538726806641</v>
       </c>
       <c r="J7" t="n">
-        <v>9.606076240539551</v>
+        <v>7.777829647064209</v>
       </c>
       <c r="K7" t="n">
-        <v>8.809288263320923</v>
+        <v>10.37955355644226</v>
       </c>
       <c r="L7" t="n">
-        <v>9.616549539566041</v>
+        <v>8.801558613777161</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>7.736706495285034</v>
+        <v>8.052810907363892</v>
       </c>
       <c r="C8" t="n">
-        <v>8.952937126159668</v>
+        <v>8.673792600631714</v>
       </c>
       <c r="D8" t="n">
-        <v>7.73447322845459</v>
+        <v>9.288197040557861</v>
       </c>
       <c r="E8" t="n">
-        <v>7.518097162246704</v>
+        <v>9.214278936386108</v>
       </c>
       <c r="F8" t="n">
-        <v>7.71428108215332</v>
+        <v>8.425323009490967</v>
       </c>
       <c r="G8" t="n">
-        <v>7.921498537063599</v>
+        <v>8.28206205368042</v>
       </c>
       <c r="H8" t="n">
-        <v>7.677603244781494</v>
+        <v>8.866334438323975</v>
       </c>
       <c r="I8" t="n">
-        <v>7.987045049667358</v>
+        <v>9.420807361602783</v>
       </c>
       <c r="J8" t="n">
-        <v>9.64812183380127</v>
+        <v>9.897531747817993</v>
       </c>
       <c r="K8" t="n">
-        <v>8.449548959732056</v>
+        <v>8.874998569488525</v>
       </c>
       <c r="L8" t="n">
-        <v>8.134031271934509</v>
+        <v>8.899613666534425</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>8.792431592941284</v>
+        <v>9.754776477813721</v>
       </c>
       <c r="C9" t="n">
-        <v>8.27428936958313</v>
+        <v>8.57709527015686</v>
       </c>
       <c r="D9" t="n">
-        <v>9.702229499816895</v>
+        <v>7.604917287826538</v>
       </c>
       <c r="E9" t="n">
-        <v>9.725714921951294</v>
+        <v>7.75725531578064</v>
       </c>
       <c r="F9" t="n">
-        <v>8.777329921722412</v>
+        <v>9.200604915618896</v>
       </c>
       <c r="G9" t="n">
-        <v>7.864469051361084</v>
+        <v>9.647561311721802</v>
       </c>
       <c r="H9" t="n">
-        <v>9.217459201812744</v>
+        <v>9.15700364112854</v>
       </c>
       <c r="I9" t="n">
-        <v>8.469658374786377</v>
+        <v>7.867403268814087</v>
       </c>
       <c r="J9" t="n">
-        <v>8.399005889892578</v>
+        <v>8.378646373748779</v>
       </c>
       <c r="K9" t="n">
-        <v>9.515436410903931</v>
+        <v>7.724343299865723</v>
       </c>
       <c r="L9" t="n">
-        <v>8.873802423477173</v>
+        <v>8.566960716247559</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>7.842961311340332</v>
+        <v>8.280855178833008</v>
       </c>
       <c r="C10" t="n">
-        <v>7.818325996398926</v>
+        <v>7.280674695968628</v>
       </c>
       <c r="D10" t="n">
-        <v>7.917590618133545</v>
+        <v>8.951656579971313</v>
       </c>
       <c r="E10" t="n">
-        <v>7.938108921051025</v>
+        <v>7.59671425819397</v>
       </c>
       <c r="F10" t="n">
-        <v>7.661656141281128</v>
+        <v>8.46220850944519</v>
       </c>
       <c r="G10" t="n">
-        <v>7.851741790771484</v>
+        <v>8.232321500778198</v>
       </c>
       <c r="H10" t="n">
-        <v>7.623882532119751</v>
+        <v>6.584391355514526</v>
       </c>
       <c r="I10" t="n">
-        <v>8.214577674865723</v>
+        <v>6.877523422241211</v>
       </c>
       <c r="J10" t="n">
-        <v>7.778202056884766</v>
+        <v>7.628637790679932</v>
       </c>
       <c r="K10" t="n">
-        <v>8.252094030380249</v>
+        <v>7.256593942642212</v>
       </c>
       <c r="L10" t="n">
-        <v>7.889914107322693</v>
+        <v>7.715157723426818</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>8.694045066833496</v>
+        <v>7.222684860229492</v>
       </c>
       <c r="C11" t="n">
-        <v>8.3551185131073</v>
+        <v>8.762439012527466</v>
       </c>
       <c r="D11" t="n">
-        <v>9.42052960395813</v>
+        <v>7.330125093460083</v>
       </c>
       <c r="E11" t="n">
-        <v>7.902743339538574</v>
+        <v>6.707775831222534</v>
       </c>
       <c r="F11" t="n">
-        <v>8.257140636444092</v>
+        <v>6.929510116577148</v>
       </c>
       <c r="G11" t="n">
-        <v>7.495041370391846</v>
+        <v>6.553633689880371</v>
       </c>
       <c r="H11" t="n">
-        <v>7.974849700927734</v>
+        <v>6.972505807876587</v>
       </c>
       <c r="I11" t="n">
-        <v>10.12043356895447</v>
+        <v>7.908141851425171</v>
       </c>
       <c r="J11" t="n">
-        <v>7.616193532943726</v>
+        <v>6.405672550201416</v>
       </c>
       <c r="K11" t="n">
-        <v>7.893957614898682</v>
+        <v>8.10735559463501</v>
       </c>
       <c r="L11" t="n">
-        <v>8.373005294799805</v>
+        <v>7.289984440803527</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>10.03680157661438</v>
+        <v>7.174556016921997</v>
       </c>
       <c r="C12" t="n">
-        <v>7.649859428405762</v>
+        <v>7.588754177093506</v>
       </c>
       <c r="D12" t="n">
-        <v>8.965606927871704</v>
+        <v>8.2639000415802</v>
       </c>
       <c r="E12" t="n">
-        <v>8.964247941970825</v>
+        <v>7.849940299987793</v>
       </c>
       <c r="F12" t="n">
-        <v>7.90969443321228</v>
+        <v>7.804153919219971</v>
       </c>
       <c r="G12" t="n">
-        <v>8.683166742324829</v>
+        <v>7.436403512954712</v>
       </c>
       <c r="H12" t="n">
-        <v>8.624203681945801</v>
+        <v>7.168666124343872</v>
       </c>
       <c r="I12" t="n">
-        <v>8.387095928192139</v>
+        <v>7.912873506546021</v>
       </c>
       <c r="J12" t="n">
-        <v>10.18274664878845</v>
+        <v>9.830746650695801</v>
       </c>
       <c r="K12" t="n">
-        <v>8.282788038253784</v>
+        <v>7.501070737838745</v>
       </c>
       <c r="L12" t="n">
-        <v>8.768621134757996</v>
+        <v>7.853106498718262</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>8.56576681137085</v>
+        <v>8.713434457778931</v>
       </c>
       <c r="C13" t="n">
-        <v>7.213509321212769</v>
+        <v>7.517938137054443</v>
       </c>
       <c r="D13" t="n">
-        <v>7.850236654281616</v>
+        <v>7.575741052627563</v>
       </c>
       <c r="E13" t="n">
-        <v>7.587634801864624</v>
+        <v>7.424476146697998</v>
       </c>
       <c r="F13" t="n">
-        <v>8.215276718139648</v>
+        <v>6.94309663772583</v>
       </c>
       <c r="G13" t="n">
-        <v>7.726164102554321</v>
+        <v>8.506783723831177</v>
       </c>
       <c r="H13" t="n">
-        <v>8.182925939559937</v>
+        <v>8.685709238052368</v>
       </c>
       <c r="I13" t="n">
-        <v>8.178835868835449</v>
+        <v>8.566137313842773</v>
       </c>
       <c r="J13" t="n">
-        <v>7.550623178482056</v>
+        <v>8.505772590637207</v>
       </c>
       <c r="K13" t="n">
-        <v>8.153689622879028</v>
+        <v>8.613236904144287</v>
       </c>
       <c r="L13" t="n">
-        <v>7.92246630191803</v>
+        <v>8.105232620239258</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>8.918340444564819</v>
+        <v>9.989223480224609</v>
       </c>
       <c r="C14" t="n">
-        <v>8.856100559234619</v>
+        <v>9.505592107772827</v>
       </c>
       <c r="D14" t="n">
-        <v>8.482524633407593</v>
+        <v>7.683491230010986</v>
       </c>
       <c r="E14" t="n">
-        <v>9.948318719863892</v>
+        <v>8.826303720474243</v>
       </c>
       <c r="F14" t="n">
-        <v>9.264147996902466</v>
+        <v>10.07657837867737</v>
       </c>
       <c r="G14" t="n">
-        <v>9.840365886688232</v>
+        <v>9.420715093612671</v>
       </c>
       <c r="H14" t="n">
-        <v>8.551522493362427</v>
+        <v>8.755747079849243</v>
       </c>
       <c r="I14" t="n">
-        <v>8.347726821899414</v>
+        <v>8.107368946075439</v>
       </c>
       <c r="J14" t="n">
-        <v>10.33447074890137</v>
+        <v>9.123601198196411</v>
       </c>
       <c r="K14" t="n">
-        <v>9.470301866531372</v>
+        <v>8.486836910247803</v>
       </c>
       <c r="L14" t="n">
-        <v>9.20138201713562</v>
+        <v>8.99754581451416</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>10.61317706108093</v>
+        <v>9.997265338897705</v>
       </c>
       <c r="C15" t="n">
-        <v>8.489818572998047</v>
+        <v>9.959241628646851</v>
       </c>
       <c r="D15" t="n">
-        <v>8.951136350631714</v>
+        <v>9.291891813278198</v>
       </c>
       <c r="E15" t="n">
-        <v>10.07532572746277</v>
+        <v>10.65653324127197</v>
       </c>
       <c r="F15" t="n">
-        <v>8.045634984970093</v>
+        <v>8.475679636001587</v>
       </c>
       <c r="G15" t="n">
-        <v>10.33550214767456</v>
+        <v>8.384468793869019</v>
       </c>
       <c r="H15" t="n">
-        <v>8.268962383270264</v>
+        <v>8.876883029937744</v>
       </c>
       <c r="I15" t="n">
-        <v>10.35714221000671</v>
+        <v>8.97361421585083</v>
       </c>
       <c r="J15" t="n">
-        <v>8.265471458435059</v>
+        <v>11.07503485679626</v>
       </c>
       <c r="K15" t="n">
-        <v>10.96875500679016</v>
+        <v>9.613198280334473</v>
       </c>
       <c r="L15" t="n">
-        <v>9.437092590332032</v>
+        <v>9.530381083488464</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>9.536369323730469</v>
+        <v>8.728075265884399</v>
       </c>
       <c r="C16" t="n">
-        <v>6.807249307632446</v>
+        <v>7.550275325775146</v>
       </c>
       <c r="D16" t="n">
-        <v>9.694525241851807</v>
+        <v>10.1579487323761</v>
       </c>
       <c r="E16" t="n">
-        <v>8.525171041488647</v>
+        <v>7.854576349258423</v>
       </c>
       <c r="F16" t="n">
-        <v>8.027706623077393</v>
+        <v>7.655609846115112</v>
       </c>
       <c r="G16" t="n">
-        <v>7.265434503555298</v>
+        <v>7.453068971633911</v>
       </c>
       <c r="H16" t="n">
-        <v>8.060376167297363</v>
+        <v>8.687689304351807</v>
       </c>
       <c r="I16" t="n">
-        <v>7.238948106765747</v>
+        <v>7.5428626537323</v>
       </c>
       <c r="J16" t="n">
-        <v>9.07909107208252</v>
+        <v>7.317914247512817</v>
       </c>
       <c r="K16" t="n">
-        <v>7.767384052276611</v>
+        <v>7.778235673904419</v>
       </c>
       <c r="L16" t="n">
-        <v>8.200225543975829</v>
+        <v>8.072625637054443</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>8.812315464019775</v>
+        <v>7.934226274490356</v>
       </c>
       <c r="C17" t="n">
-        <v>8.01884388923645</v>
+        <v>9.278257369995117</v>
       </c>
       <c r="D17" t="n">
-        <v>9.573880910873413</v>
+        <v>8.030524730682373</v>
       </c>
       <c r="E17" t="n">
-        <v>8.258946180343628</v>
+        <v>8.52520227432251</v>
       </c>
       <c r="F17" t="n">
-        <v>8.895222902297974</v>
+        <v>10.59865713119507</v>
       </c>
       <c r="G17" t="n">
-        <v>9.364836931228638</v>
+        <v>8.352215766906738</v>
       </c>
       <c r="H17" t="n">
-        <v>9.53960919380188</v>
+        <v>8.661632061004639</v>
       </c>
       <c r="I17" t="n">
-        <v>8.853492498397827</v>
+        <v>8.991981029510498</v>
       </c>
       <c r="J17" t="n">
-        <v>10.18351364135742</v>
+        <v>8.15519118309021</v>
       </c>
       <c r="K17" t="n">
-        <v>7.666447877883911</v>
+        <v>7.853320360183716</v>
       </c>
       <c r="L17" t="n">
-        <v>8.916710948944091</v>
+        <v>8.638120818138123</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>9.185423374176025</v>
+        <v>10.00424647331238</v>
       </c>
       <c r="C18" t="n">
-        <v>8.788935661315918</v>
+        <v>9.040822744369507</v>
       </c>
       <c r="D18" t="n">
-        <v>10.57373309135437</v>
+        <v>10.76844382286072</v>
       </c>
       <c r="E18" t="n">
-        <v>9.538142204284668</v>
+        <v>9.067790031433105</v>
       </c>
       <c r="F18" t="n">
-        <v>9.680210113525391</v>
+        <v>9.527262926101685</v>
       </c>
       <c r="G18" t="n">
-        <v>10.14150810241699</v>
+        <v>9.740949869155884</v>
       </c>
       <c r="H18" t="n">
-        <v>10.19580745697021</v>
+        <v>8.815425634384155</v>
       </c>
       <c r="I18" t="n">
-        <v>9.33222222328186</v>
+        <v>10.6229202747345</v>
       </c>
       <c r="J18" t="n">
-        <v>9.857064008712769</v>
+        <v>9.862034797668457</v>
       </c>
       <c r="K18" t="n">
-        <v>10.27289795875549</v>
+        <v>12.81589412689209</v>
       </c>
       <c r="L18" t="n">
-        <v>9.75659441947937</v>
+        <v>10.02657907009125</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>9.203686714172363</v>
+        <v>7.697324514389038</v>
       </c>
       <c r="C19" t="n">
-        <v>7.477353096008301</v>
+        <v>7.08600378036499</v>
       </c>
       <c r="D19" t="n">
-        <v>7.566854000091553</v>
+        <v>7.544879198074341</v>
       </c>
       <c r="E19" t="n">
-        <v>8.613619804382324</v>
+        <v>6.431060314178467</v>
       </c>
       <c r="F19" t="n">
-        <v>8.405342578887939</v>
+        <v>8.634945631027222</v>
       </c>
       <c r="G19" t="n">
-        <v>8.414607286453247</v>
+        <v>6.701080083847046</v>
       </c>
       <c r="H19" t="n">
-        <v>8.927325487136841</v>
+        <v>7.244115829467773</v>
       </c>
       <c r="I19" t="n">
-        <v>7.5810706615448</v>
+        <v>7.828730583190918</v>
       </c>
       <c r="J19" t="n">
-        <v>7.099075555801392</v>
+        <v>7.009002208709717</v>
       </c>
       <c r="K19" t="n">
-        <v>6.907437801361084</v>
+        <v>8.78753662109375</v>
       </c>
       <c r="L19" t="n">
-        <v>8.019637298583984</v>
+        <v>7.496467876434326</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>8.209913730621338</v>
+        <v>11.35806226730347</v>
       </c>
       <c r="C20" t="n">
-        <v>8.530523300170898</v>
+        <v>9.248321533203125</v>
       </c>
       <c r="D20" t="n">
-        <v>8.691092014312744</v>
+        <v>11.04720544815063</v>
       </c>
       <c r="E20" t="n">
-        <v>9.460061073303223</v>
+        <v>7.845666646957397</v>
       </c>
       <c r="F20" t="n">
-        <v>9.646206140518188</v>
+        <v>9.004952192306519</v>
       </c>
       <c r="G20" t="n">
-        <v>7.963204860687256</v>
+        <v>7.165242433547974</v>
       </c>
       <c r="H20" t="n">
-        <v>8.547180652618408</v>
+        <v>10.01628017425537</v>
       </c>
       <c r="I20" t="n">
-        <v>7.964687347412109</v>
+        <v>8.178800582885742</v>
       </c>
       <c r="J20" t="n">
-        <v>8.67516040802002</v>
+        <v>7.971640825271606</v>
       </c>
       <c r="K20" t="n">
-        <v>8.27643609046936</v>
+        <v>7.742329835891724</v>
       </c>
       <c r="L20" t="n">
-        <v>8.596446561813355</v>
+        <v>8.957850193977356</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>10.37897968292236</v>
+        <v>8.13353419303894</v>
       </c>
       <c r="C21" t="n">
-        <v>10.45307612419128</v>
+        <v>9.533104181289673</v>
       </c>
       <c r="D21" t="n">
-        <v>7.98855447769165</v>
+        <v>9.144465446472168</v>
       </c>
       <c r="E21" t="n">
-        <v>8.822980403900146</v>
+        <v>9.654061555862427</v>
       </c>
       <c r="F21" t="n">
-        <v>8.151047945022583</v>
+        <v>9.674128532409668</v>
       </c>
       <c r="G21" t="n">
-        <v>8.773314952850342</v>
+        <v>8.112305879592896</v>
       </c>
       <c r="H21" t="n">
-        <v>8.691086530685425</v>
+        <v>6.890573024749756</v>
       </c>
       <c r="I21" t="n">
-        <v>8.252625465393066</v>
+        <v>7.516851663589478</v>
       </c>
       <c r="J21" t="n">
-        <v>8.96204400062561</v>
+        <v>8.018556356430054</v>
       </c>
       <c r="K21" t="n">
-        <v>10.23829317092896</v>
+        <v>8.085378646850586</v>
       </c>
       <c r="L21" t="n">
-        <v>9.071200275421143</v>
+        <v>8.476295948028564</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>8.669511318206787</v>
+        <v>7.521885395050049</v>
       </c>
       <c r="C22" t="n">
-        <v>8.805048704147339</v>
+        <v>6.831729412078857</v>
       </c>
       <c r="D22" t="n">
-        <v>8.511616706848145</v>
+        <v>8.757580280303955</v>
       </c>
       <c r="E22" t="n">
-        <v>9.207079887390137</v>
+        <v>8.2309889793396</v>
       </c>
       <c r="F22" t="n">
-        <v>9.180213689804077</v>
+        <v>8.43643856048584</v>
       </c>
       <c r="G22" t="n">
-        <v>8.429737567901611</v>
+        <v>8.64189076423645</v>
       </c>
       <c r="H22" t="n">
-        <v>7.607921123504639</v>
+        <v>7.618625402450562</v>
       </c>
       <c r="I22" t="n">
-        <v>8.011716365814209</v>
+        <v>7.142898082733154</v>
       </c>
       <c r="J22" t="n">
-        <v>7.263355493545532</v>
+        <v>7.843026161193848</v>
       </c>
       <c r="K22" t="n">
-        <v>8.585160255432129</v>
+        <v>9.036834478378296</v>
       </c>
       <c r="L22" t="n">
-        <v>8.427136111259461</v>
+        <v>8.006189751625062</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>9.703940391540527</v>
+        <v>9.189425468444824</v>
       </c>
       <c r="C23" t="n">
-        <v>9.381742000579834</v>
+        <v>8.866288900375366</v>
       </c>
       <c r="D23" t="n">
-        <v>8.979367971420288</v>
+        <v>8.498273849487305</v>
       </c>
       <c r="E23" t="n">
-        <v>10.01592063903809</v>
+        <v>8.332716226577759</v>
       </c>
       <c r="F23" t="n">
-        <v>9.629659652709961</v>
+        <v>8.38557505607605</v>
       </c>
       <c r="G23" t="n">
-        <v>9.10617208480835</v>
+        <v>8.312769651412964</v>
       </c>
       <c r="H23" t="n">
-        <v>10.56913709640503</v>
+        <v>8.222012519836426</v>
       </c>
       <c r="I23" t="n">
-        <v>8.894103765487671</v>
+        <v>8.71968150138855</v>
       </c>
       <c r="J23" t="n">
-        <v>9.898301124572754</v>
+        <v>9.335036993026733</v>
       </c>
       <c r="K23" t="n">
-        <v>9.043720006942749</v>
+        <v>9.196406602859497</v>
       </c>
       <c r="L23" t="n">
-        <v>9.522206473350526</v>
+        <v>8.705818676948548</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>9.719470977783203</v>
+        <v>8.382582664489746</v>
       </c>
       <c r="C24" t="n">
-        <v>8.879609346389771</v>
+        <v>8.478327512741089</v>
       </c>
       <c r="D24" t="n">
-        <v>7.389398813247681</v>
+        <v>7.305463790893555</v>
       </c>
       <c r="E24" t="n">
-        <v>8.261948823928833</v>
+        <v>7.971682071685791</v>
       </c>
       <c r="F24" t="n">
-        <v>8.533361196517944</v>
+        <v>7.339373350143433</v>
       </c>
       <c r="G24" t="n">
-        <v>8.090331554412842</v>
+        <v>7.905857801437378</v>
       </c>
       <c r="H24" t="n">
-        <v>10.29747986793518</v>
+        <v>7.455062866210938</v>
       </c>
       <c r="I24" t="n">
-        <v>8.28931450843811</v>
+        <v>7.124946117401123</v>
       </c>
       <c r="J24" t="n">
-        <v>8.788040161132812</v>
+        <v>7.325409650802612</v>
       </c>
       <c r="K24" t="n">
-        <v>8.959622859954834</v>
+        <v>8.325735807418823</v>
       </c>
       <c r="L24" t="n">
-        <v>8.72085781097412</v>
+        <v>7.761444163322449</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>11.15093564987183</v>
+        <v>10.1099636554718</v>
       </c>
       <c r="C25" t="n">
-        <v>9.107718706130981</v>
+        <v>9.64121675491333</v>
       </c>
       <c r="D25" t="n">
-        <v>9.457235336303711</v>
+        <v>10.37724947929382</v>
       </c>
       <c r="E25" t="n">
-        <v>10.22736740112305</v>
+        <v>9.645206212997437</v>
       </c>
       <c r="F25" t="n">
-        <v>9.846664428710938</v>
+        <v>8.938097953796387</v>
       </c>
       <c r="G25" t="n">
-        <v>9.138236284255981</v>
+        <v>9.092684268951416</v>
       </c>
       <c r="H25" t="n">
-        <v>9.658349752426147</v>
+        <v>9.272204637527466</v>
       </c>
       <c r="I25" t="n">
-        <v>10.79451704025269</v>
+        <v>10.38722252845764</v>
       </c>
       <c r="J25" t="n">
-        <v>8.380044937133789</v>
+        <v>9.266220808029175</v>
       </c>
       <c r="K25" t="n">
-        <v>10.1398913860321</v>
+        <v>9.202390193939209</v>
       </c>
       <c r="L25" t="n">
-        <v>9.790096092224122</v>
+        <v>9.593245649337769</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>8.525649547576904</v>
+        <v>9.467680931091309</v>
       </c>
       <c r="C26" t="n">
-        <v>8.999026298522949</v>
+        <v>7.645553350448608</v>
       </c>
       <c r="D26" t="n">
-        <v>10.03878140449524</v>
+        <v>9.576391458511353</v>
       </c>
       <c r="E26" t="n">
-        <v>10.14518404006958</v>
+        <v>9.350993394851685</v>
       </c>
       <c r="F26" t="n">
-        <v>9.628176689147949</v>
+        <v>8.305788993835449</v>
       </c>
       <c r="G26" t="n">
-        <v>7.926986455917358</v>
+        <v>8.611970186233521</v>
       </c>
       <c r="H26" t="n">
-        <v>8.785987615585327</v>
+        <v>8.194414615631104</v>
       </c>
       <c r="I26" t="n">
-        <v>9.005674362182617</v>
+        <v>7.809116840362549</v>
       </c>
       <c r="J26" t="n">
-        <v>8.42651891708374</v>
+        <v>8.931116819381714</v>
       </c>
       <c r="K26" t="n">
-        <v>10.53746724128723</v>
+        <v>8.5980064868927</v>
       </c>
       <c r="L26" t="n">
-        <v>9.201945257186889</v>
+        <v>8.649103307723999</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>10.71953392028809</v>
+        <v>9.6721351146698</v>
       </c>
       <c r="C27" t="n">
-        <v>8.769480466842651</v>
+        <v>8.68976092338562</v>
       </c>
       <c r="D27" t="n">
-        <v>10.11796617507935</v>
+        <v>9.778850078582764</v>
       </c>
       <c r="E27" t="n">
-        <v>10.1054162979126</v>
+        <v>8.506251811981201</v>
       </c>
       <c r="F27" t="n">
-        <v>10.60953521728516</v>
+        <v>10.04114842414856</v>
       </c>
       <c r="G27" t="n">
-        <v>10.96296215057373</v>
+        <v>8.637900352478027</v>
       </c>
       <c r="H27" t="n">
-        <v>11.23341751098633</v>
+        <v>8.436439037322998</v>
       </c>
       <c r="I27" t="n">
-        <v>9.352678298950195</v>
+        <v>8.561105489730835</v>
       </c>
       <c r="J27" t="n">
-        <v>8.660088539123535</v>
+        <v>8.057453393936157</v>
       </c>
       <c r="K27" t="n">
-        <v>10.52528595924377</v>
+        <v>8.38657283782959</v>
       </c>
       <c r="L27" t="n">
-        <v>10.10563645362854</v>
+        <v>8.876761746406554</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>7.94368314743042</v>
+        <v>8.311771869659424</v>
       </c>
       <c r="C28" t="n">
-        <v>8.243701457977295</v>
+        <v>8.425468683242798</v>
       </c>
       <c r="D28" t="n">
-        <v>8.816292762756348</v>
+        <v>7.822436332702637</v>
       </c>
       <c r="E28" t="n">
-        <v>10.14475107192993</v>
+        <v>7.037180185317993</v>
       </c>
       <c r="F28" t="n">
-        <v>9.680089712142944</v>
+        <v>7.103004932403564</v>
       </c>
       <c r="G28" t="n">
-        <v>9.768857717514038</v>
+        <v>7.90685510635376</v>
       </c>
       <c r="H28" t="n">
-        <v>7.675550937652588</v>
+        <v>8.634908199310303</v>
       </c>
       <c r="I28" t="n">
-        <v>8.011139631271362</v>
+        <v>8.414498567581177</v>
       </c>
       <c r="J28" t="n">
-        <v>8.997882127761841</v>
+        <v>9.825724124908447</v>
       </c>
       <c r="K28" t="n">
-        <v>9.699256420135498</v>
+        <v>7.754262447357178</v>
       </c>
       <c r="L28" t="n">
-        <v>8.898120498657226</v>
+        <v>8.123611044883727</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>9.731817007064819</v>
+        <v>7.767229080200195</v>
       </c>
       <c r="C29" t="n">
-        <v>10.70537662506104</v>
+        <v>7.076076745986938</v>
       </c>
       <c r="D29" t="n">
-        <v>8.920595645904541</v>
+        <v>7.769223690032959</v>
       </c>
       <c r="E29" t="n">
-        <v>8.357054233551025</v>
+        <v>7.125943899154663</v>
       </c>
       <c r="F29" t="n">
-        <v>8.911674976348877</v>
+        <v>7.516898632049561</v>
       </c>
       <c r="G29" t="n">
-        <v>9.475109577178955</v>
+        <v>7.126940965652466</v>
       </c>
       <c r="H29" t="n">
-        <v>8.635280609130859</v>
+        <v>7.543826818466187</v>
       </c>
       <c r="I29" t="n">
-        <v>8.817303657531738</v>
+        <v>9.607307910919189</v>
       </c>
       <c r="J29" t="n">
-        <v>8.024191379547119</v>
+        <v>7.97866415977478</v>
       </c>
       <c r="K29" t="n">
-        <v>8.683228731155396</v>
+        <v>7.314439296722412</v>
       </c>
       <c r="L29" t="n">
-        <v>9.026163244247437</v>
+        <v>7.682655119895935</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>8.162944793701172</v>
+        <v>7.956722497940063</v>
       </c>
       <c r="C30" t="n">
-        <v>9.361616611480713</v>
+        <v>7.685447454452515</v>
       </c>
       <c r="D30" t="n">
-        <v>7.791385412216187</v>
+        <v>8.38058876991272</v>
       </c>
       <c r="E30" t="n">
-        <v>9.571617364883423</v>
+        <v>6.750945806503296</v>
       </c>
       <c r="F30" t="n">
-        <v>9.22597074508667</v>
+        <v>8.321746349334717</v>
       </c>
       <c r="G30" t="n">
-        <v>8.291971683502197</v>
+        <v>7.06510591506958</v>
       </c>
       <c r="H30" t="n">
-        <v>8.400803327560425</v>
+        <v>6.9853196144104</v>
       </c>
       <c r="I30" t="n">
-        <v>9.094449758529663</v>
+        <v>7.282525062561035</v>
       </c>
       <c r="J30" t="n">
-        <v>8.091581583023071</v>
+        <v>8.709708213806152</v>
       </c>
       <c r="K30" t="n">
-        <v>7.788937568664551</v>
+        <v>7.680461406707764</v>
       </c>
       <c r="L30" t="n">
-        <v>8.578127884864807</v>
+        <v>7.681857109069824</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>8.790764808654785</v>
+        <v>8.799468278884888</v>
       </c>
       <c r="C31" t="n">
-        <v>7.496867418289185</v>
+        <v>7.928797006607056</v>
       </c>
       <c r="D31" t="n">
-        <v>8.11736011505127</v>
+        <v>8.854331493377686</v>
       </c>
       <c r="E31" t="n">
-        <v>9.267699241638184</v>
+        <v>8.771543025970459</v>
       </c>
       <c r="F31" t="n">
-        <v>8.600790739059448</v>
+        <v>8.500268459320068</v>
       </c>
       <c r="G31" t="n">
-        <v>7.765359878540039</v>
+        <v>7.819089651107788</v>
       </c>
       <c r="H31" t="n">
-        <v>7.463250160217285</v>
+        <v>9.148535013198853</v>
       </c>
       <c r="I31" t="n">
-        <v>8.791889667510986</v>
+        <v>10.28457450866699</v>
       </c>
       <c r="J31" t="n">
-        <v>7.462142944335938</v>
+        <v>8.626726627349854</v>
       </c>
       <c r="K31" t="n">
-        <v>7.584250688552856</v>
+        <v>10.68576097488403</v>
       </c>
       <c r="L31" t="n">
-        <v>8.134037566184997</v>
+        <v>8.941909503936767</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>10.05051350593567</v>
+        <v>12.31816220283508</v>
       </c>
       <c r="C32" t="n">
-        <v>11.67150902748108</v>
+        <v>11.03253054618835</v>
       </c>
       <c r="D32" t="n">
-        <v>8.607389450073242</v>
+        <v>13.89581537246704</v>
       </c>
       <c r="E32" t="n">
-        <v>10.72396421432495</v>
+        <v>14.88775992393494</v>
       </c>
       <c r="F32" t="n">
-        <v>8.482209920883179</v>
+        <v>14.4914436340332</v>
       </c>
       <c r="G32" t="n">
-        <v>9.904292583465576</v>
+        <v>15.65376257896423</v>
       </c>
       <c r="H32" t="n">
-        <v>8.842109680175781</v>
+        <v>11.72587966918945</v>
       </c>
       <c r="I32" t="n">
-        <v>9.811077356338501</v>
+        <v>11.141193151474</v>
       </c>
       <c r="J32" t="n">
-        <v>9.651768922805786</v>
+        <v>11.3763256072998</v>
       </c>
       <c r="K32" t="n">
-        <v>10.56254601478577</v>
+        <v>11.60096764564514</v>
       </c>
       <c r="L32" t="n">
-        <v>9.830738067626953</v>
+        <v>12.81238403320313</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>8.498751878738403</v>
+        <v>7.745121955871582</v>
       </c>
       <c r="C33" t="n">
-        <v>8.615458011627197</v>
+        <v>9.585393667221069</v>
       </c>
       <c r="D33" t="n">
-        <v>7.367270469665527</v>
+        <v>17.89998030662537</v>
       </c>
       <c r="E33" t="n">
-        <v>7.77489185333252</v>
+        <v>10.85974168777466</v>
       </c>
       <c r="F33" t="n">
-        <v>7.826617956161499</v>
+        <v>8.60139274597168</v>
       </c>
       <c r="G33" t="n">
-        <v>8.074257850646973</v>
+        <v>12.46212673187256</v>
       </c>
       <c r="H33" t="n">
-        <v>8.52860951423645</v>
+        <v>12.20488452911377</v>
       </c>
       <c r="I33" t="n">
-        <v>8.187304973602295</v>
+        <v>7.527374267578125</v>
       </c>
       <c r="J33" t="n">
-        <v>7.931089878082275</v>
+        <v>7.855737209320068</v>
       </c>
       <c r="K33" t="n">
-        <v>9.146034717559814</v>
+        <v>9.856679677963257</v>
       </c>
       <c r="L33" t="n">
-        <v>8.195028710365296</v>
+        <v>10.45984327793121</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>10.42210054397583</v>
+        <v>10.12999176979065</v>
       </c>
       <c r="C34" t="n">
-        <v>8.224247217178345</v>
+        <v>10.72635412216187</v>
       </c>
       <c r="D34" t="n">
-        <v>11.42529082298279</v>
+        <v>9.217350006103516</v>
       </c>
       <c r="E34" t="n">
-        <v>9.861120700836182</v>
+        <v>7.607336759567261</v>
       </c>
       <c r="F34" t="n">
-        <v>8.956604719161987</v>
+        <v>11.60702848434448</v>
       </c>
       <c r="G34" t="n">
-        <v>9.092801332473755</v>
+        <v>8.388755083084106</v>
       </c>
       <c r="H34" t="n">
-        <v>9.798705816268921</v>
+        <v>7.799022436141968</v>
       </c>
       <c r="I34" t="n">
-        <v>11.07602691650391</v>
+        <v>9.057919025421143</v>
       </c>
       <c r="J34" t="n">
-        <v>8.742143869400024</v>
+        <v>10.66152191162109</v>
       </c>
       <c r="K34" t="n">
-        <v>9.354466438293457</v>
+        <v>8.391559362411499</v>
       </c>
       <c r="L34" t="n">
-        <v>9.695350837707519</v>
+        <v>9.358683896064758</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>9.232233762741089</v>
+        <v>8.362114906311035</v>
       </c>
       <c r="C35" t="n">
-        <v>9.232757329940796</v>
+        <v>8.572075843811035</v>
       </c>
       <c r="D35" t="n">
-        <v>9.057436943054199</v>
+        <v>9.152570247650146</v>
       </c>
       <c r="E35" t="n">
-        <v>8.228661775588989</v>
+        <v>7.860953330993652</v>
       </c>
       <c r="F35" t="n">
-        <v>9.35125732421875</v>
+        <v>7.637611627578735</v>
       </c>
       <c r="G35" t="n">
-        <v>9.280061006546021</v>
+        <v>7.422224998474121</v>
       </c>
       <c r="H35" t="n">
-        <v>8.661290407180786</v>
+        <v>8.133380889892578</v>
       </c>
       <c r="I35" t="n">
-        <v>8.000234603881836</v>
+        <v>9.031364679336548</v>
       </c>
       <c r="J35" t="n">
-        <v>9.182375431060791</v>
+        <v>7.756557464599609</v>
       </c>
       <c r="K35" t="n">
-        <v>9.569330453872681</v>
+        <v>10.21769285202026</v>
       </c>
       <c r="L35" t="n">
-        <v>8.979563903808593</v>
+        <v>8.414654684066772</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>8.424196720123291</v>
+        <v>8.042284250259399</v>
       </c>
       <c r="C36" t="n">
-        <v>9.521803379058838</v>
+        <v>7.980987310409546</v>
       </c>
       <c r="D36" t="n">
-        <v>8.22300386428833</v>
+        <v>9.47668981552124</v>
       </c>
       <c r="E36" t="n">
-        <v>8.073043584823608</v>
+        <v>9.701785802841187</v>
       </c>
       <c r="F36" t="n">
-        <v>9.764962673187256</v>
+        <v>10.22569298744202</v>
       </c>
       <c r="G36" t="n">
-        <v>7.832170009613037</v>
+        <v>9.363326787948608</v>
       </c>
       <c r="H36" t="n">
-        <v>8.862778186798096</v>
+        <v>10.97165870666504</v>
       </c>
       <c r="I36" t="n">
-        <v>7.910957813262939</v>
+        <v>9.884996891021729</v>
       </c>
       <c r="J36" t="n">
-        <v>9.868342399597168</v>
+        <v>8.883557081222534</v>
       </c>
       <c r="K36" t="n">
-        <v>9.256408929824829</v>
+        <v>9.150404930114746</v>
       </c>
       <c r="L36" t="n">
-        <v>8.773766756057739</v>
+        <v>9.368138456344605</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>8.717657089233398</v>
+        <v>8.752593994140625</v>
       </c>
       <c r="C37" t="n">
-        <v>8.899473905563354</v>
+        <v>7.47700572013855</v>
       </c>
       <c r="D37" t="n">
-        <v>8.585701465606689</v>
+        <v>8.21152138710022</v>
       </c>
       <c r="E37" t="n">
-        <v>8.86283016204834</v>
+        <v>8.056478977203369</v>
       </c>
       <c r="F37" t="n">
-        <v>7.906652450561523</v>
+        <v>7.322415113449097</v>
       </c>
       <c r="G37" t="n">
-        <v>9.131881475448608</v>
+        <v>7.526839733123779</v>
       </c>
       <c r="H37" t="n">
-        <v>9.466160297393799</v>
+        <v>9.146477937698364</v>
       </c>
       <c r="I37" t="n">
-        <v>9.838806867599487</v>
+        <v>7.443820714950562</v>
       </c>
       <c r="J37" t="n">
-        <v>9.470030069351196</v>
+        <v>7.219291687011719</v>
       </c>
       <c r="K37" t="n">
-        <v>7.873607158660889</v>
+        <v>7.671348571777344</v>
       </c>
       <c r="L37" t="n">
-        <v>8.875280094146728</v>
+        <v>7.882779383659363</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>8.288325071334839</v>
+        <v>8.213036775588989</v>
       </c>
       <c r="C38" t="n">
-        <v>7.88447117805481</v>
+        <v>7.445238590240479</v>
       </c>
       <c r="D38" t="n">
-        <v>8.792561769485474</v>
+        <v>7.517030715942383</v>
       </c>
       <c r="E38" t="n">
-        <v>8.134506702423096</v>
+        <v>7.340370655059814</v>
       </c>
       <c r="F38" t="n">
-        <v>8.995115518569946</v>
+        <v>7.374573469161987</v>
       </c>
       <c r="G38" t="n">
-        <v>8.296003341674805</v>
+        <v>7.4251868724823</v>
       </c>
       <c r="H38" t="n">
-        <v>8.061139345169067</v>
+        <v>7.517444610595703</v>
       </c>
       <c r="I38" t="n">
-        <v>8.184493780136108</v>
+        <v>7.372995853424072</v>
       </c>
       <c r="J38" t="n">
-        <v>7.931313991546631</v>
+        <v>8.726382493972778</v>
       </c>
       <c r="K38" t="n">
-        <v>7.690598011016846</v>
+        <v>7.027995824813843</v>
       </c>
       <c r="L38" t="n">
-        <v>8.225852870941162</v>
+        <v>7.596025586128235</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>8.473021507263184</v>
+        <v>7.980806350708008</v>
       </c>
       <c r="C39" t="n">
-        <v>8.990777015686035</v>
+        <v>9.7370285987854</v>
       </c>
       <c r="D39" t="n">
-        <v>8.8703293800354</v>
+        <v>9.091326713562012</v>
       </c>
       <c r="E39" t="n">
-        <v>9.598929643630981</v>
+        <v>7.933782815933228</v>
       </c>
       <c r="F39" t="n">
-        <v>7.651092767715454</v>
+        <v>8.684643745422363</v>
       </c>
       <c r="G39" t="n">
-        <v>7.919912815093994</v>
+        <v>8.157182693481445</v>
       </c>
       <c r="H39" t="n">
-        <v>7.811844348907471</v>
+        <v>7.900871515274048</v>
       </c>
       <c r="I39" t="n">
-        <v>7.740500926971436</v>
+        <v>7.982644557952881</v>
       </c>
       <c r="J39" t="n">
-        <v>9.402514934539795</v>
+        <v>8.918816328048706</v>
       </c>
       <c r="K39" t="n">
-        <v>8.441989421844482</v>
+        <v>8.212448835372925</v>
       </c>
       <c r="L39" t="n">
-        <v>8.490091276168823</v>
+        <v>8.459955215454102</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>9.171753883361816</v>
+        <v>7.744969606399536</v>
       </c>
       <c r="C40" t="n">
-        <v>8.050966262817383</v>
+        <v>8.602229356765747</v>
       </c>
       <c r="D40" t="n">
-        <v>8.859388113021851</v>
+        <v>7.386852264404297</v>
       </c>
       <c r="E40" t="n">
-        <v>7.385166645050049</v>
+        <v>8.225062847137451</v>
       </c>
       <c r="F40" t="n">
-        <v>7.622634887695312</v>
+        <v>8.462272167205811</v>
       </c>
       <c r="G40" t="n">
-        <v>7.565187454223633</v>
+        <v>9.552013158798218</v>
       </c>
       <c r="H40" t="n">
-        <v>7.67799186706543</v>
+        <v>8.294886350631714</v>
       </c>
       <c r="I40" t="n">
-        <v>9.188596963882446</v>
+        <v>8.026350975036621</v>
       </c>
       <c r="J40" t="n">
-        <v>7.236545324325562</v>
+        <v>9.023856401443481</v>
       </c>
       <c r="K40" t="n">
-        <v>9.655398368835449</v>
+        <v>9.351233959197998</v>
       </c>
       <c r="L40" t="n">
-        <v>8.241362977027894</v>
+        <v>8.466972708702087</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>7.650983572006226</v>
+        <v>9.083708763122559</v>
       </c>
       <c r="C41" t="n">
-        <v>7.721296548843384</v>
+        <v>8.651863098144531</v>
       </c>
       <c r="D41" t="n">
-        <v>8.017138004302979</v>
+        <v>8.127609729766846</v>
       </c>
       <c r="E41" t="n">
-        <v>8.512346982955933</v>
+        <v>7.538839817047119</v>
       </c>
       <c r="F41" t="n">
-        <v>8.080952644348145</v>
+        <v>9.026859998703003</v>
       </c>
       <c r="G41" t="n">
-        <v>7.748823404312134</v>
+        <v>8.591216564178467</v>
       </c>
       <c r="H41" t="n">
-        <v>7.526953935623169</v>
+        <v>8.721786499023438</v>
       </c>
       <c r="I41" t="n">
-        <v>7.771265745162964</v>
+        <v>8.494430303573608</v>
       </c>
       <c r="J41" t="n">
-        <v>9.63613224029541</v>
+        <v>8.988023042678833</v>
       </c>
       <c r="K41" t="n">
-        <v>8.237156629562378</v>
+        <v>8.930175542831421</v>
       </c>
       <c r="L41" t="n">
-        <v>8.090304970741272</v>
+        <v>8.615451335906982</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>7.599627733230591</v>
+        <v>9.202375650405884</v>
       </c>
       <c r="C42" t="n">
-        <v>8.356205224990845</v>
+        <v>9.052823781967163</v>
       </c>
       <c r="D42" t="n">
-        <v>8.874467611312866</v>
+        <v>8.0257408618927</v>
       </c>
       <c r="E42" t="n">
-        <v>7.993615388870239</v>
+        <v>8.065073251724243</v>
       </c>
       <c r="F42" t="n">
-        <v>7.680951833724976</v>
+        <v>8.80045223236084</v>
       </c>
       <c r="G42" t="n">
-        <v>9.427987337112427</v>
+        <v>7.217572927474976</v>
       </c>
       <c r="H42" t="n">
-        <v>7.735815048217773</v>
+        <v>7.712428569793701</v>
       </c>
       <c r="I42" t="n">
-        <v>8.501822948455811</v>
+        <v>8.784508466720581</v>
       </c>
       <c r="J42" t="n">
-        <v>8.361196756362915</v>
+        <v>8.915159225463867</v>
       </c>
       <c r="K42" t="n">
-        <v>8.159208536148071</v>
+        <v>8.670812845230103</v>
       </c>
       <c r="L42" t="n">
-        <v>8.269089841842652</v>
+        <v>8.444694781303406</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>7.792631864547729</v>
+        <v>8.747606754302979</v>
       </c>
       <c r="C43" t="n">
-        <v>8.106836795806885</v>
+        <v>7.596685171127319</v>
       </c>
       <c r="D43" t="n">
-        <v>8.913782835006714</v>
+        <v>7.316949844360352</v>
       </c>
       <c r="E43" t="n">
-        <v>7.690913438796997</v>
+        <v>7.338445901870728</v>
       </c>
       <c r="F43" t="n">
-        <v>8.142709970474243</v>
+        <v>7.623611927032471</v>
       </c>
       <c r="G43" t="n">
-        <v>7.021566867828369</v>
+        <v>7.977666616439819</v>
       </c>
       <c r="H43" t="n">
-        <v>6.841094732284546</v>
+        <v>7.345357179641724</v>
       </c>
       <c r="I43" t="n">
-        <v>7.961203813552856</v>
+        <v>8.230888366699219</v>
       </c>
       <c r="J43" t="n">
-        <v>8.008631944656372</v>
+        <v>8.025846719741821</v>
       </c>
       <c r="K43" t="n">
-        <v>8.298326015472412</v>
+        <v>8.350600957870483</v>
       </c>
       <c r="L43" t="n">
-        <v>7.877769827842712</v>
+        <v>7.855365943908692</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>8.084390878677368</v>
+        <v>7.27036714553833</v>
       </c>
       <c r="C44" t="n">
-        <v>8.192132472991943</v>
+        <v>7.856252193450928</v>
       </c>
       <c r="D44" t="n">
-        <v>6.766762256622314</v>
+        <v>6.484658718109131</v>
       </c>
       <c r="E44" t="n">
-        <v>8.535750389099121</v>
+        <v>7.240612506866455</v>
       </c>
       <c r="F44" t="n">
-        <v>7.462993860244751</v>
+        <v>6.363033294677734</v>
       </c>
       <c r="G44" t="n">
-        <v>7.605600118637085</v>
+        <v>6.622337102890015</v>
       </c>
       <c r="H44" t="n">
-        <v>6.939828872680664</v>
+        <v>6.753938674926758</v>
       </c>
       <c r="I44" t="n">
-        <v>8.662413835525513</v>
+        <v>8.418610095977783</v>
       </c>
       <c r="J44" t="n">
-        <v>7.188672065734863</v>
+        <v>7.488972663879395</v>
       </c>
       <c r="K44" t="n">
-        <v>7.487933158874512</v>
+        <v>6.885586023330688</v>
       </c>
       <c r="L44" t="n">
-        <v>7.692647790908813</v>
+        <v>7.138436841964722</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>8.470924139022827</v>
+        <v>9.987290859222412</v>
       </c>
       <c r="C45" t="n">
-        <v>9.700765609741211</v>
+        <v>10.13888692855835</v>
       </c>
       <c r="D45" t="n">
-        <v>8.936719655990601</v>
+        <v>9.085702419281006</v>
       </c>
       <c r="E45" t="n">
-        <v>8.446449995040894</v>
+        <v>8.718684434890747</v>
       </c>
       <c r="F45" t="n">
-        <v>9.425959348678589</v>
+        <v>10.45703601837158</v>
       </c>
       <c r="G45" t="n">
-        <v>9.698794364929199</v>
+        <v>9.283174276351929</v>
       </c>
       <c r="H45" t="n">
-        <v>8.203179597854614</v>
+        <v>9.42878532409668</v>
       </c>
       <c r="I45" t="n">
-        <v>8.319286108016968</v>
+        <v>11.88621354103088</v>
       </c>
       <c r="J45" t="n">
-        <v>8.275883913040161</v>
+        <v>8.634908676147461</v>
       </c>
       <c r="K45" t="n">
-        <v>8.729256868362427</v>
+        <v>9.402221918106079</v>
       </c>
       <c r="L45" t="n">
-        <v>8.820721960067749</v>
+        <v>9.702290439605713</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>6.938348293304443</v>
+        <v>8.2639000415802</v>
       </c>
       <c r="C46" t="n">
-        <v>8.749242544174194</v>
+        <v>9.011900186538696</v>
       </c>
       <c r="D46" t="n">
-        <v>7.380214691162109</v>
+        <v>6.892568588256836</v>
       </c>
       <c r="E46" t="n">
-        <v>6.643090963363647</v>
+        <v>9.068747758865356</v>
       </c>
       <c r="F46" t="n">
-        <v>8.874414920806885</v>
+        <v>7.143895864486694</v>
       </c>
       <c r="G46" t="n">
-        <v>7.935762643814087</v>
+        <v>8.067425727844238</v>
       </c>
       <c r="H46" t="n">
-        <v>7.567214250564575</v>
+        <v>8.03950023651123</v>
       </c>
       <c r="I46" t="n">
-        <v>8.312336921691895</v>
+        <v>8.110311031341553</v>
       </c>
       <c r="J46" t="n">
-        <v>6.892926454544067</v>
+        <v>6.930466175079346</v>
       </c>
       <c r="K46" t="n">
-        <v>7.364755868911743</v>
+        <v>9.407841682434082</v>
       </c>
       <c r="L46" t="n">
-        <v>7.665830755233765</v>
+        <v>8.093655729293824</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>9.662889719009399</v>
+        <v>10.2795102596283</v>
       </c>
       <c r="C47" t="n">
-        <v>12.56272840499878</v>
+        <v>8.288833618164062</v>
       </c>
       <c r="D47" t="n">
-        <v>10.04595041275024</v>
+        <v>7.990631103515625</v>
       </c>
       <c r="E47" t="n">
-        <v>8.856812238693237</v>
+        <v>10.78666138648987</v>
       </c>
       <c r="F47" t="n">
-        <v>10.53795981407166</v>
+        <v>11.24173140525818</v>
       </c>
       <c r="G47" t="n">
-        <v>11.12168025970459</v>
+        <v>9.819751977920532</v>
       </c>
       <c r="H47" t="n">
-        <v>8.984056949615479</v>
+        <v>9.276826858520508</v>
       </c>
       <c r="I47" t="n">
-        <v>9.28309965133667</v>
+        <v>9.422213554382324</v>
       </c>
       <c r="J47" t="n">
-        <v>9.008060932159424</v>
+        <v>8.862313747406006</v>
       </c>
       <c r="K47" t="n">
-        <v>9.542259454727173</v>
+        <v>10.04206299781799</v>
       </c>
       <c r="L47" t="n">
-        <v>9.960549783706664</v>
+        <v>9.601053690910339</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>8.089954614639282</v>
+        <v>7.156860589981079</v>
       </c>
       <c r="C48" t="n">
-        <v>9.05580735206604</v>
+        <v>6.862648487091064</v>
       </c>
       <c r="D48" t="n">
-        <v>7.251036882400513</v>
+        <v>6.548530101776123</v>
       </c>
       <c r="E48" t="n">
-        <v>7.14370584487915</v>
+        <v>7.215828657150269</v>
       </c>
       <c r="F48" t="n">
-        <v>8.123924493789673</v>
+        <v>7.413259506225586</v>
       </c>
       <c r="G48" t="n">
-        <v>8.265280246734619</v>
+        <v>8.005043268203735</v>
       </c>
       <c r="H48" t="n">
-        <v>7.358575344085693</v>
+        <v>6.828923463821411</v>
       </c>
       <c r="I48" t="n">
-        <v>10.35573053359985</v>
+        <v>9.53291916847229</v>
       </c>
       <c r="J48" t="n">
-        <v>7.230175018310547</v>
+        <v>9.341635465621948</v>
       </c>
       <c r="K48" t="n">
-        <v>7.110984325408936</v>
+        <v>11.46440720558167</v>
       </c>
       <c r="L48" t="n">
-        <v>7.998517465591431</v>
+        <v>8.037005591392518</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>8.046553134918213</v>
+        <v>9.078758955001831</v>
       </c>
       <c r="C49" t="n">
-        <v>7.928305864334106</v>
+        <v>10.5671865940094</v>
       </c>
       <c r="D49" t="n">
-        <v>7.28203821182251</v>
+        <v>9.827941179275513</v>
       </c>
       <c r="E49" t="n">
-        <v>9.141238212585449</v>
+        <v>7.617628812789917</v>
       </c>
       <c r="F49" t="n">
-        <v>9.188627004623413</v>
+        <v>9.458164215087891</v>
       </c>
       <c r="G49" t="n">
-        <v>8.700928211212158</v>
+        <v>8.32295036315918</v>
       </c>
       <c r="H49" t="n">
-        <v>8.296446800231934</v>
+        <v>9.167462110519409</v>
       </c>
       <c r="I49" t="n">
-        <v>7.83604907989502</v>
+        <v>9.630282640457153</v>
       </c>
       <c r="J49" t="n">
-        <v>7.443013668060303</v>
+        <v>7.517895460128784</v>
       </c>
       <c r="K49" t="n">
-        <v>8.951235771179199</v>
+        <v>7.704688787460327</v>
       </c>
       <c r="L49" t="n">
-        <v>8.28144359588623</v>
+        <v>8.88929591178894</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>7.797594785690308</v>
+        <v>9.926163673400879</v>
       </c>
       <c r="C50" t="n">
-        <v>7.823934316635132</v>
+        <v>10.59119415283203</v>
       </c>
       <c r="D50" t="n">
-        <v>9.339670896530151</v>
+        <v>8.853820085525513</v>
       </c>
       <c r="E50" t="n">
-        <v>7.848011255264282</v>
+        <v>9.126733303070068</v>
       </c>
       <c r="F50" t="n">
-        <v>8.286392211914062</v>
+        <v>8.291237831115723</v>
       </c>
       <c r="G50" t="n">
-        <v>8.874385833740234</v>
+        <v>9.676321029663086</v>
       </c>
       <c r="H50" t="n">
-        <v>8.094918489456177</v>
+        <v>8.798456907272339</v>
       </c>
       <c r="I50" t="n">
-        <v>8.830481767654419</v>
+        <v>8.577062606811523</v>
       </c>
       <c r="J50" t="n">
-        <v>10.28031039237976</v>
+        <v>8.808382511138916</v>
       </c>
       <c r="K50" t="n">
-        <v>8.023567914962769</v>
+        <v>8.857313394546509</v>
       </c>
       <c r="L50" t="n">
-        <v>8.519926786422729</v>
+        <v>9.150668549537659</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>9.025986433029175</v>
+        <v>8.447245359420776</v>
       </c>
       <c r="C51" t="n">
-        <v>7.728805303573608</v>
+        <v>8.294954538345337</v>
       </c>
       <c r="D51" t="n">
-        <v>7.915334463119507</v>
+        <v>8.038907289505005</v>
       </c>
       <c r="E51" t="n">
-        <v>6.733325481414795</v>
+        <v>7.257129192352295</v>
       </c>
       <c r="F51" t="n">
-        <v>7.434053182601929</v>
+        <v>7.938222169876099</v>
       </c>
       <c r="G51" t="n">
-        <v>10.48376846313477</v>
+        <v>7.877040147781372</v>
       </c>
       <c r="H51" t="n">
-        <v>7.285959243774414</v>
+        <v>8.428683757781982</v>
       </c>
       <c r="I51" t="n">
-        <v>7.168226718902588</v>
+        <v>7.360358238220215</v>
       </c>
       <c r="J51" t="n">
-        <v>7.275945425033569</v>
+        <v>6.894562959671021</v>
       </c>
       <c r="K51" t="n">
-        <v>7.842994451522827</v>
+        <v>7.188594579696655</v>
       </c>
       <c r="L51" t="n">
-        <v>7.889439916610717</v>
+        <v>7.772569823265076</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>8.849400658607482</v>
+        <v>8.744465346336364</v>
       </c>
       <c r="C52" t="n">
-        <v>8.738960824012757</v>
+        <v>8.551467871665954</v>
       </c>
       <c r="D52" t="n">
-        <v>8.715626583099365</v>
+        <v>8.830982375144959</v>
       </c>
       <c r="E52" t="n">
-        <v>8.784301161766052</v>
+        <v>8.447470107078551</v>
       </c>
       <c r="F52" t="n">
-        <v>8.68617118358612</v>
+        <v>8.701033487319947</v>
       </c>
       <c r="G52" t="n">
-        <v>8.783936591148377</v>
+        <v>8.450373511314393</v>
       </c>
       <c r="H52" t="n">
-        <v>8.540662159919739</v>
+        <v>8.465558152198792</v>
       </c>
       <c r="I52" t="n">
-        <v>8.687936611175537</v>
+        <v>8.590014038085938</v>
       </c>
       <c r="J52" t="n">
-        <v>8.583777589797974</v>
+        <v>8.556322407722472</v>
       </c>
       <c r="K52" t="n">
-        <v>8.762450470924378</v>
+        <v>8.740420107841492</v>
       </c>
       <c r="L52" t="n">
-        <v>8.71332238340378</v>
+        <v>8.607810740470887</v>
       </c>
     </row>
   </sheetData>
